--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -244,8 +244,14 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -280,6 +286,11 @@
         <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008EA9DB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="44">
     <border>
@@ -840,7 +851,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1122,6 +1133,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2019,193 +2033,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="70" min="1" max="1"/>
-    <col width="70" customWidth="1" style="70" min="2" max="2"/>
-    <col width="40" customWidth="1" style="70" min="3" max="3"/>
+    <col width="72" customWidth="1" style="70" min="2" max="2"/>
+    <col width="42" customWidth="1" style="70" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="70">
       <c r="A1" s="99" t="inlineStr">
         <is>
-          <t>中核人材ペルソナ（技術者後継者像）案　～江口逸夫氏（工場長）のキャリアをベンチマーク～</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" s="70">
+          <t>中核人材ペルソナ（技術者後継者像）案　～江口逸夫氏（取締役 本社工場長）本人インタビューに基づく～</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1" s="70">
       <c r="A2" s="100" t="inlineStr">
         <is>
-          <t>※第2回コンサルティング（中核人材ペルソナ設計と採用基準の言語化）での使用を想定した素案。事実関係はコンサルタントとのすり合わせの上、確定してください。</t>
+          <t>※第2回コンサルティング（中核人材ペルソナ設計と採用基準の言語化）での使用を想定した素案。本人インタビュー（選択式）の回答をもとに作成。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" s="70">
-      <c r="A3" s="101" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
+        <is>
+          <t>【正確な経歴】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="70">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B3" s="101" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>要件・内容</t>
         </is>
       </c>
-      <c r="C3" s="101" t="inlineStr">
-        <is>
-          <t>根拠（江口氏のキャリアより）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55" customHeight="1" s="70">
-      <c r="A4" s="102" t="inlineStr">
-        <is>
-          <t>学歴</t>
-        </is>
-      </c>
-      <c r="B4" s="103" t="inlineStr">
-        <is>
-          <t>工学系（材料工学・金属工学・機械材料系）修士以上。博士（工学）は歓迎条件（必須ではない）</t>
-        </is>
-      </c>
-      <c r="C4" s="103" t="inlineStr">
-        <is>
-          <t>2014～2015年頃、宇都宮大学にて博士号を取得（本人申告）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55" customHeight="1" s="70">
+      <c r="C4" s="101" t="inlineStr">
+        <is>
+          <t>根拠（本人インタビューより）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1" s="70">
       <c r="A5" s="102" t="inlineStr">
         <is>
-          <t>専門分野</t>
+          <t>キャリアパス</t>
         </is>
       </c>
       <c r="B5" s="103" t="inlineStr">
         <is>
-          <t>非鉄金属材料、銅合金（特に高強度・高導電性合金）、金属組織学、塑性加工</t>
+          <t>製造 → 品質保証 → 製造 → 製品開発課 → 朝霞工場長 → 取締役 本社工場長</t>
         </is>
       </c>
       <c r="C5" s="103" t="inlineStr">
         <is>
-          <t>特許JP2008223069A「高強度高導電性銅合金及びその製造方法」発明者の一人（出願人：三芳合金工業株式会社）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55" customHeight="1" s="70">
+          <t>本人申告（従来案にあった「製造→営業→開発」の記載は誤りのため訂正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="70">
       <c r="A6" s="102" t="inlineStr">
         <is>
-          <t>研究開発志向</t>
+          <t>入社時の学歴</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>実務課題を特許出願・学会発表・論文化など学術的に体系化した経験</t>
+          <t>修士卒で入社。その後、在籍しながら社会人学生として博士号（宇都宮大学）を取得</t>
         </is>
       </c>
       <c r="C6" s="103" t="inlineStr">
         <is>
-          <t>上記特許および博士研究を、現場の実務課題から着想・体系化した実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55" customHeight="1" s="70">
-      <c r="A7" s="102" t="inlineStr">
-        <is>
-          <t>現場理解力</t>
-        </is>
-      </c>
-      <c r="B7" s="103" t="inlineStr">
-        <is>
-          <t>製造（生産技術）→営業→開発、のように複数部門を横断した経験、または経験する意欲</t>
-        </is>
-      </c>
-      <c r="C7" s="103" t="inlineStr">
-        <is>
-          <t>1995年入社後、製造課→営業課（3年目以降）→製品開発課（係長）という複数部門を経験</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55" customHeight="1" s="70">
-      <c r="A8" s="102" t="inlineStr">
-        <is>
-          <t>育成タイムライン（目安）</t>
-        </is>
-      </c>
-      <c r="B8" s="103" t="inlineStr">
-        <is>
-          <t>入社後3年：製造・現場理解／5～10年：営業・技術営業で顧客ニーズを吸収／10～20年：開発課で中核技術者として自立</t>
-        </is>
-      </c>
-      <c r="C8" s="103" t="inlineStr">
-        <is>
-          <t>江口氏自身のキャリアパスを、後継者育成の標準モデルとして言語化</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55" customHeight="1" s="70">
-      <c r="A9" s="102" t="inlineStr">
-        <is>
-          <t>保有資格・実績の目安</t>
-        </is>
-      </c>
-      <c r="B9" s="103" t="inlineStr">
-        <is>
-          <t>金属材料系の学会所属、技術士（金属部門）等の専門資格があれば尚可</t>
-        </is>
-      </c>
-      <c r="C9" s="103" t="inlineStr">
-        <is>
-          <t>（要確認：江口氏本人の学会所属・資格の棚卸しを推奨）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55" customHeight="1" s="70">
+          <t>本人申告</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="70">
+      <c r="A8" s="105" t="inlineStr">
+        <is>
+          <t>A. 学歴・研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="70">
+      <c r="A9" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B9" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C9" s="101" t="inlineStr">
+        <is>
+          <t>根拠（本人インタビューより）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" s="70">
       <c r="A10" s="102" t="inlineStr">
         <is>
-          <t>人物像・価値観</t>
+          <t>博士論文テーマ</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
-          <t>「モノづくりと同じくらいヒトづくりに全力で取り組む」という社風に共感できる人。世のため人のためという経営理念への共感</t>
+          <t>高強度・高導電性銅合金の合金設計・析出強化機構。特に「結晶粒成長をいかに抑制するか（粒界の易動度）」に注力</t>
         </is>
       </c>
       <c r="C10" s="103" t="inlineStr">
         <is>
-          <t>大和合金グループの経営理念・企業文化（社外公開情報より）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55" customHeight="1" s="70">
+          <t>本人インタビュー。特許JP2008223069A「高強度高導電性銅合金及びその製造方法」の技術系譜と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1" s="70">
       <c r="A11" s="102" t="inlineStr">
         <is>
-          <t>キャリアゴール像</t>
+          <t>進学の経緯</t>
         </is>
       </c>
       <c r="B11" s="103" t="inlineStr">
         <is>
-          <t>将来的に製品開発課をリードし、必要に応じて社会人博士課程等で技術を体系化・発信できる人材</t>
+          <t>社長の人脈による縁、かつ宇都宮大学で非鉄金属の研究が行われていたことが理由</t>
         </is>
       </c>
       <c r="C11" s="103" t="inlineStr">
         <is>
-          <t>江口氏の「現場叩き上げ→技術を学術的に体系化」というロールモデルの再現</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1" s="70">
-      <c r="A12" s="104" t="inlineStr">
-        <is>
-          <t>【要確認事項】博士学位論文の正式タイトル・取得年度（2014年 or 2015年）・専攻分野は、学位記または宇都宮大学への照会で確定し、本表を更新してください。</t>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" s="70">
+      <c r="A12" s="102" t="inlineStr">
+        <is>
+          <t>在学形態</t>
+        </is>
+      </c>
+      <c r="B12" s="103" t="inlineStr">
+        <is>
+          <t>会社に在籍しながら社会人学生として博士号を取得（休職・離職はなし）</t>
+        </is>
+      </c>
+      <c r="C12" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="70">
+      <c r="A14" s="105" t="inlineStr">
+        <is>
+          <t>B. キャリアの転機</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="70">
+      <c r="A15" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B15" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C15" s="101" t="inlineStr">
+        <is>
+          <t>根拠（本人インタビューより）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1" s="70">
+      <c r="A16" s="102" t="inlineStr">
+        <is>
+          <t>異動の経緯</t>
+        </is>
+      </c>
+      <c r="B16" s="103" t="inlineStr">
+        <is>
+          <t>基本的に会社の人事方針・組織上の必要による異動</t>
+        </is>
+      </c>
+      <c r="C16" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1" s="70">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>ターニングポイント</t>
+        </is>
+      </c>
+      <c r="B17" s="103" t="inlineStr">
+        <is>
+          <t>朝霞工場長時代、大手企業の研究員・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただし、それは現場のモノづくりを広く経験した基盤があってこそ</t>
+        </is>
+      </c>
+      <c r="C17" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="70">
+      <c r="A19" s="105" t="inlineStr">
+        <is>
+          <t>C. 技術者としての専門性</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="70">
+      <c r="A20" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B20" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C20" s="101" t="inlineStr">
+        <is>
+          <t>根拠（本人インタビューより）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="55" customHeight="1" s="70">
+      <c r="A21" s="102" t="inlineStr">
+        <is>
+          <t>現在の強み</t>
+        </is>
+      </c>
+      <c r="B21" s="103" t="inlineStr">
+        <is>
+          <t>① 製造・品質・開発の全部門を俯瞰した技術判断力
+② 外部（大手企業・国の研究機関）と対等に議論できる専門性・発信力</t>
+        </is>
+      </c>
+      <c r="C21" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1" s="70">
+      <c r="A22" s="102" t="inlineStr">
+        <is>
+          <t>暗黙知・勘所</t>
+        </is>
+      </c>
+      <c r="B22" s="103" t="inlineStr">
+        <is>
+          <t>不良・異常の兆候を先取りして見抜く力（10～20年かけて培われる現場感覚）</t>
+        </is>
+      </c>
+      <c r="C22" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="70">
+      <c r="A24" s="105" t="inlineStr">
+        <is>
+          <t>D. 後継者に求める資質</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="70">
+      <c r="A25" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B25" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C25" s="101" t="inlineStr">
+        <is>
+          <t>根拠（本人インタビューより）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1" s="70">
+      <c r="A26" s="102" t="inlineStr">
+        <is>
+          <t>必須の資質（優先順位順）</t>
+        </is>
+      </c>
+      <c r="B26" s="103" t="inlineStr">
+        <is>
+          <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢（現場主義）　＞　③立場の違う人と対等に議論できる度胸</t>
+        </is>
+      </c>
+      <c r="C26" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1" s="70">
+      <c r="A27" s="102" t="inlineStr">
+        <is>
+          <t>「任せられる」と判断する決め手</t>
+        </is>
+      </c>
+      <c r="B27" s="103" t="inlineStr">
+        <is>
+          <t>失敗への向き合い方（逃げずに原因を追究できるか）</t>
+        </is>
+      </c>
+      <c r="C27" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1" s="70">
+      <c r="A28" s="102" t="inlineStr">
+        <is>
+          <t>NG条件</t>
+        </is>
+      </c>
+      <c r="B28" s="103" t="inlineStr">
+        <is>
+          <t>都合の悪い情報を隠す・報告を遅らせる姿勢</t>
+        </is>
+      </c>
+      <c r="C28" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1" s="70">
+      <c r="A29" s="102" t="inlineStr">
+        <is>
+          <t>有効だった育成環境</t>
+        </is>
+      </c>
+      <c r="B29" s="103" t="inlineStr">
+        <is>
+          <t>外部の研究者・他社との共同開発の機会を与えられたこと</t>
+        </is>
+      </c>
+      <c r="C29" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" s="70">
+      <c r="A31" s="105" t="inlineStr">
+        <is>
+          <t>E. 企業文化・組織</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="70">
+      <c r="A32" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B32" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C32" s="101" t="inlineStr">
+        <is>
+          <t>根拠（本人インタビューより）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1" s="70">
+      <c r="A33" s="102" t="inlineStr">
+        <is>
+          <t>大和合金ならではの文化</t>
+        </is>
+      </c>
+      <c r="B33" s="103" t="inlineStr">
+        <is>
+          <t>「モノづくりと同じくらいヒトづくり」を本気で重視する社風</t>
+        </is>
+      </c>
+      <c r="C33" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー／社外公開情報とも一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1" s="70">
+      <c r="A35" s="104" t="inlineStr">
+        <is>
+          <t>【要確認事項】博士学位論文の正式タイトル・取得年度（2014年 or 2015年）は、学位記または宇都宮大学への照会で確定し、本表を更新してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -292,7 +292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -841,6 +841,50 @@
       <bottom style="thin">
         <color rgb="00808080"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
@@ -2033,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="70" min="1" max="1"/>
@@ -2041,17 +2085,17 @@
     <col width="42" customWidth="1" style="70" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="70">
+    <row r="1" ht="34" customHeight="1" s="70">
       <c r="A1" s="99" t="inlineStr">
         <is>
-          <t>中核人材ペルソナ（技術者後継者像）案　～江口逸夫氏（取締役 本社工場長）本人インタビューに基づく～</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1" s="70">
+          <t>中核人材ペルソナ（技術者後継者像）案　～江口逸夫氏（取締役 本社工場長）本人インタビュー＋製品開発課の理念資料に基づく～</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1" s="70">
       <c r="A2" s="100" t="inlineStr">
         <is>
-          <t>※第2回コンサルティング（中核人材ペルソナ設計と採用基準の言語化）での使用を想定した素案。本人インタビュー（選択式）の回答をもとに作成。</t>
+          <t>※第2回コンサルティング（中核人材ペルソナ設計と採用基準の言語化）での使用を想定した素案。本人インタビューおよび「製品開発課の理念」「ミッション・ビジョン・バリュー」「何を成果とみなすか」の社内資料をもとに作成。</t>
         </is>
       </c>
     </row>
@@ -2075,11 +2119,11 @@
       </c>
       <c r="C4" s="101" t="inlineStr">
         <is>
-          <t>根拠（本人インタビューより）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1" s="70">
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1" s="70">
       <c r="A5" s="102" t="inlineStr">
         <is>
           <t>キャリアパス</t>
@@ -2092,11 +2136,11 @@
       </c>
       <c r="C5" s="103" t="inlineStr">
         <is>
-          <t>本人申告（従来案にあった「製造→営業→開発」の記載は誤りのため訂正）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1" s="70">
+          <t>本人申告</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1" s="70">
       <c r="A6" s="102" t="inlineStr">
         <is>
           <t>入社時の学歴</t>
@@ -2133,11 +2177,11 @@
       </c>
       <c r="C9" s="101" t="inlineStr">
         <is>
-          <t>根拠（本人インタビューより）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1" s="70">
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1" s="70">
       <c r="A10" s="102" t="inlineStr">
         <is>
           <t>博士論文テーマ</t>
@@ -2154,15 +2198,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1" s="70">
+    <row r="11" ht="50" customHeight="1" s="70">
       <c r="A11" s="102" t="inlineStr">
         <is>
-          <t>進学の経緯</t>
+          <t>進学の経緯／在学形態</t>
         </is>
       </c>
       <c r="B11" s="103" t="inlineStr">
         <is>
-          <t>社長の人脈による縁、かつ宇都宮大学で非鉄金属の研究が行われていたことが理由</t>
+          <t>社長の人脈による縁、かつ宇都宮大学で非鉄金属の研究が行われていたことが理由。会社に在籍しながら社会人学生として取得（休職・離職なし）</t>
         </is>
       </c>
       <c r="C11" s="103" t="inlineStr">
@@ -2171,190 +2215,190 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1" s="70">
-      <c r="A12" s="102" t="inlineStr">
-        <is>
-          <t>在学形態</t>
-        </is>
-      </c>
-      <c r="B12" s="103" t="inlineStr">
-        <is>
-          <t>会社に在籍しながら社会人学生として博士号を取得（休職・離職はなし）</t>
-        </is>
-      </c>
-      <c r="C12" s="103" t="inlineStr">
+    <row r="13" ht="22" customHeight="1" s="70">
+      <c r="A13" s="105" t="inlineStr">
+        <is>
+          <t>B. キャリアの転機（朝霞工場長時代の具体的実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="70">
+      <c r="A14" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B14" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C14" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1" s="70">
+      <c r="A15" s="102" t="inlineStr">
+        <is>
+          <t>実績①：現場改革</t>
+        </is>
+      </c>
+      <c r="B15" s="103" t="inlineStr">
+        <is>
+          <t>朝霞工場で2S活動・生産性改善を主導。現場の意識改革（毎日の2Sを習慣化する文化づくり）により、過去最高の出荷重量を「当たり前」に出せる体制を実現。最大の苦労は短期的な生産優先との時間配分バランス</t>
+        </is>
+      </c>
+      <c r="C15" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" s="70">
-      <c r="A14" s="105" t="inlineStr">
-        <is>
-          <t>B. キャリアの転機</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="70">
-      <c r="A15" s="101" t="inlineStr">
+    <row r="16" ht="65" customHeight="1" s="70">
+      <c r="A16" s="102" t="inlineStr">
+        <is>
+          <t>実績②：国家プロジェクト級の共同開発</t>
+        </is>
+      </c>
+      <c r="B16" s="103" t="inlineStr">
+        <is>
+          <t>核融合炉（ITER＝国際熱核融合実験炉）向け銅合金の開発で、国の研究機関の研究員と対等に議論しながら新製品化。同分野で大和合金グループは世界供給量No.1の実績を保有</t>
+        </is>
+      </c>
+      <c r="C16" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー＋社内ビジョン資料（製品開発課のビジョン：ITER採用実績）との一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1" s="70">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>実績③：大手企業との共同開発</t>
+        </is>
+      </c>
+      <c r="B17" s="103" t="inlineStr">
+        <is>
+          <t>すべり軸受・耐摩耗部品向けの新合金開発で大手企業と連携（社内実績として、航空機ランディングギア用銅合金メタルブッシュは世界シェア20%でトップレベル）</t>
+        </is>
+      </c>
+      <c r="C17" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー＋社内ビジョン資料との整合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1" s="70">
+      <c r="A18" s="102" t="inlineStr">
+        <is>
+          <t>ターニングポイントの本質</t>
+        </is>
+      </c>
+      <c r="B18" s="103" t="inlineStr">
+        <is>
+          <t>大手企業・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただしそれは、現場のモノづくりを広く経験した基盤があってこそ</t>
+        </is>
+      </c>
+      <c r="C18" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="70">
+      <c r="A20" s="105" t="inlineStr">
+        <is>
+          <t>C. 技術者としての専門性</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="70">
+      <c r="A21" s="101" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B15" s="101" t="inlineStr">
+      <c r="B21" s="101" t="inlineStr">
         <is>
           <t>要件・内容</t>
         </is>
       </c>
-      <c r="C15" s="101" t="inlineStr">
-        <is>
-          <t>根拠（本人インタビューより）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1" s="70">
-      <c r="A16" s="102" t="inlineStr">
-        <is>
-          <t>異動の経緯</t>
-        </is>
-      </c>
-      <c r="B16" s="103" t="inlineStr">
-        <is>
-          <t>基本的に会社の人事方針・組織上の必要による異動</t>
-        </is>
-      </c>
-      <c r="C16" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1" s="70">
-      <c r="A17" s="102" t="inlineStr">
-        <is>
-          <t>ターニングポイント</t>
-        </is>
-      </c>
-      <c r="B17" s="103" t="inlineStr">
-        <is>
-          <t>朝霞工場長時代、大手企業の研究員・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただし、それは現場のモノづくりを広く経験した基盤があってこそ</t>
-        </is>
-      </c>
-      <c r="C17" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="70">
-      <c r="A19" s="105" t="inlineStr">
-        <is>
-          <t>C. 技術者としての専門性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" s="70">
-      <c r="A20" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B20" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C20" s="101" t="inlineStr">
-        <is>
-          <t>根拠（本人インタビューより）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="55" customHeight="1" s="70">
-      <c r="A21" s="102" t="inlineStr">
+      <c r="C21" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1" s="70">
+      <c r="A22" s="102" t="inlineStr">
         <is>
           <t>現在の強み</t>
         </is>
       </c>
-      <c r="B21" s="103" t="inlineStr">
+      <c r="B22" s="103" t="inlineStr">
         <is>
           <t>① 製造・品質・開発の全部門を俯瞰した技術判断力
 ② 外部（大手企業・国の研究機関）と対等に議論できる専門性・発信力</t>
         </is>
       </c>
-      <c r="C21" s="103" t="inlineStr">
+      <c r="C22" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1" s="70">
-      <c r="A22" s="102" t="inlineStr">
+    <row r="23" ht="45" customHeight="1" s="70">
+      <c r="A23" s="102" t="inlineStr">
         <is>
           <t>暗黙知・勘所</t>
         </is>
       </c>
-      <c r="B22" s="103" t="inlineStr">
+      <c r="B23" s="103" t="inlineStr">
         <is>
           <t>不良・異常の兆候を先取りして見抜く力（10～20年かけて培われる現場感覚）</t>
         </is>
       </c>
-      <c r="C22" s="103" t="inlineStr">
+      <c r="C23" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1" s="70">
-      <c r="A24" s="105" t="inlineStr">
+    <row r="25" ht="22" customHeight="1" s="70">
+      <c r="A25" s="105" t="inlineStr">
         <is>
           <t>D. 後継者に求める資質</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1" s="70">
-      <c r="A25" s="101" t="inlineStr">
+    <row r="26" ht="20" customHeight="1" s="70">
+      <c r="A26" s="101" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B25" s="101" t="inlineStr">
+      <c r="B26" s="101" t="inlineStr">
         <is>
           <t>要件・内容</t>
         </is>
       </c>
-      <c r="C25" s="101" t="inlineStr">
-        <is>
-          <t>根拠（本人インタビューより）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="55" customHeight="1" s="70">
-      <c r="A26" s="102" t="inlineStr">
+      <c r="C26" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1" s="70">
+      <c r="A27" s="102" t="inlineStr">
         <is>
           <t>必須の資質（優先順位順）</t>
         </is>
       </c>
-      <c r="B26" s="103" t="inlineStr">
+      <c r="B27" s="103" t="inlineStr">
         <is>
           <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢（現場主義）　＞　③立場の違う人と対等に議論できる度胸</t>
-        </is>
-      </c>
-      <c r="C26" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1" s="70">
-      <c r="A27" s="102" t="inlineStr">
-        <is>
-          <t>「任せられる」と判断する決め手</t>
-        </is>
-      </c>
-      <c r="B27" s="103" t="inlineStr">
-        <is>
-          <t>失敗への向き合い方（逃げずに原因を追究できるか）</t>
         </is>
       </c>
       <c r="C27" s="103" t="inlineStr">
@@ -2366,12 +2410,12 @@
     <row r="28" ht="40" customHeight="1" s="70">
       <c r="A28" s="102" t="inlineStr">
         <is>
-          <t>NG条件</t>
+          <t>「任せられる」と判断する決め手</t>
         </is>
       </c>
       <c r="B28" s="103" t="inlineStr">
         <is>
-          <t>都合の悪い情報を隠す・報告を遅らせる姿勢</t>
+          <t>失敗への向き合い方（逃げずに原因を追究できるか）</t>
         </is>
       </c>
       <c r="C28" s="103" t="inlineStr">
@@ -2383,78 +2427,264 @@
     <row r="29" ht="40" customHeight="1" s="70">
       <c r="A29" s="102" t="inlineStr">
         <is>
+          <t>NG条件</t>
+        </is>
+      </c>
+      <c r="B29" s="103" t="inlineStr">
+        <is>
+          <t>都合の悪い情報を隠す・報告を遅らせる姿勢</t>
+        </is>
+      </c>
+      <c r="C29" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1" s="70">
+      <c r="A30" s="102" t="inlineStr">
+        <is>
           <t>有効だった育成環境</t>
         </is>
       </c>
-      <c r="B29" s="103" t="inlineStr">
+      <c r="B30" s="103" t="inlineStr">
         <is>
           <t>外部の研究者・他社との共同開発の機会を与えられたこと</t>
         </is>
       </c>
-      <c r="C29" s="103" t="inlineStr">
+      <c r="C30" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1" s="70">
-      <c r="A31" s="105" t="inlineStr">
+    <row r="32" ht="22" customHeight="1" s="70">
+      <c r="A32" s="105" t="inlineStr">
         <is>
           <t>E. 企業文化・組織</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1" s="70">
-      <c r="A32" s="101" t="inlineStr">
+    <row r="33" ht="20" customHeight="1" s="70">
+      <c r="A33" s="101" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B32" s="101" t="inlineStr">
+      <c r="B33" s="101" t="inlineStr">
         <is>
           <t>要件・内容</t>
         </is>
       </c>
-      <c r="C32" s="101" t="inlineStr">
-        <is>
-          <t>根拠（本人インタビューより）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="40" customHeight="1" s="70">
-      <c r="A33" s="102" t="inlineStr">
+      <c r="C33" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1" s="70">
+      <c r="A34" s="102" t="inlineStr">
         <is>
           <t>大和合金ならではの文化</t>
         </is>
       </c>
-      <c r="B33" s="103" t="inlineStr">
+      <c r="B34" s="103" t="inlineStr">
         <is>
           <t>「モノづくりと同じくらいヒトづくり」を本気で重視する社風</t>
         </is>
       </c>
-      <c r="C33" s="103" t="inlineStr">
+      <c r="C34" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー／社外公開情報とも一致</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1" s="70">
-      <c r="A35" s="104" t="inlineStr">
+    <row r="36" ht="22" customHeight="1" s="70">
+      <c r="A36" s="105" t="inlineStr">
+        <is>
+          <t>F. 製品開発課の理念（採用基準として明文化すべき共感ポイント）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="70">
+      <c r="A37" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B37" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C37" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1" s="70">
+      <c r="A38" s="102" t="inlineStr">
+        <is>
+          <t>ミッション</t>
+        </is>
+      </c>
+      <c r="B38" s="103" t="inlineStr">
+        <is>
+          <t>大和合金グループが永続的に世の中に貢献し続けるための仕組み（＝技術）の創出</t>
+        </is>
+      </c>
+      <c r="C38" s="103" t="inlineStr">
+        <is>
+          <t>社内資料「ミッション・ビジョン・バリュー」</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1" s="70">
+      <c r="A39" s="102" t="inlineStr">
+        <is>
+          <t>ビジョン</t>
+        </is>
+      </c>
+      <c r="B39" s="103" t="inlineStr">
+        <is>
+          <t>世界一の銅合金の専門家チーム。（実績例：半導体用バッキングプレート販売シェア世界一30%、ITER向け銅合金供給量世界一、航空機用メタルブッシュ世界トップレベル20%）</t>
+        </is>
+      </c>
+      <c r="C39" s="103" t="inlineStr">
+        <is>
+          <t>社内資料「ミッション・ビジョン・バリュー」</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="55" customHeight="1" s="70">
+      <c r="A40" s="102" t="inlineStr">
+        <is>
+          <t>バリュー（3つ）</t>
+        </is>
+      </c>
+      <c r="B40" s="103" t="inlineStr">
+        <is>
+          <t>①再現性の追求（技術的エビデンスの重視）　②記録の徹底（獲得した知見の知財化・資産化）　③完遂へのこだわり（選択と集中）</t>
+        </is>
+      </c>
+      <c r="C40" s="103" t="inlineStr">
+        <is>
+          <t>社内資料「ミッション・ビジョン・バリュー」</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="55" customHeight="1" s="70">
+      <c r="A41" s="102" t="inlineStr">
+        <is>
+          <t>採用面接での確認ポイント（提案）</t>
+        </is>
+      </c>
+      <c r="B41" s="103" t="inlineStr">
+        <is>
+          <t>上記ミッション・ビジョン・バリューへの共感度を、面接評価票の必須項目として設計することを推奨。特に「記録の徹底」「完遂へのこだわり」は行動特性として面接で見極め可能</t>
+        </is>
+      </c>
+      <c r="C41" s="103" t="inlineStr">
+        <is>
+          <t>コンサルタント提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" s="70">
+      <c r="A43" s="105" t="inlineStr">
+        <is>
+          <t>G. 何を成果とみなすか（評価基準・OJT設計への活用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="70">
+      <c r="A44" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B44" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C44" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="55" customHeight="1" s="70">
+      <c r="A45" s="102" t="inlineStr">
+        <is>
+          <t>短期成果（2～3ヶ月）</t>
+        </is>
+      </c>
+      <c r="B45" s="103" t="inlineStr">
+        <is>
+          <t>新製品・新製法開発では「仮説検証の完了数」（失敗して条件を否定できたことも成果）。既存製法改善では「標準書・手順書の改定完了件数」</t>
+        </is>
+      </c>
+      <c r="C45" s="103" t="inlineStr">
+        <is>
+          <t>社内資料「何を成果とみなすか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="55" customHeight="1" s="70">
+      <c r="A46" s="102" t="inlineStr">
+        <is>
+          <t>中期成果（半年～1年）</t>
+        </is>
+      </c>
+      <c r="B46" s="103" t="inlineStr">
+        <is>
+          <t>新製品はお客様のスペック承認・QC工程表確定の件数。新製法はパイロットテスト成功・投資判断データ完成の数。知財管理は特許出願・ノウハウ登録件数</t>
+        </is>
+      </c>
+      <c r="C46" s="103" t="inlineStr">
+        <is>
+          <t>社内資料「何を成果とみなすか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="55" customHeight="1" s="70">
+      <c r="A47" s="102" t="inlineStr">
+        <is>
+          <t>育成初期の目標設計への示唆</t>
+        </is>
+      </c>
+      <c r="B47" s="103" t="inlineStr">
+        <is>
+          <t>入社後は「仮説検証を完了させる」経験を積ませ、記録・報告の型を早期に習慣化させることが、江口氏の言う「地道な努力」「記録の徹底」の実践につながる</t>
+        </is>
+      </c>
+      <c r="C47" s="103" t="inlineStr">
+        <is>
+          <t>コンサルタント提案（本人インタビューと社内資料の統合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1" s="70">
+      <c r="A49" s="104" t="inlineStr">
         <is>
           <t>【要確認事項】博士学位論文の正式タイトル・取得年度（2014年 or 2015年）は、学位記または宇都宮大学への照会で確定し、本表を更新してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A19:C19"/>
+  <mergeCells count="11">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -895,7 +895,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1182,6 +1182,8 @@
     <xf numFmtId="0" fontId="30" fillId="7" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2105,6 +2107,8 @@
           <t>【正確な経歴】</t>
         </is>
       </c>
+      <c r="B3" s="106" t="n"/>
+      <c r="C3" s="107" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="70">
       <c r="A4" s="101" t="inlineStr">
@@ -2157,12 +2161,15 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="22" customHeight="1" s="70">
       <c r="A8" s="105" t="inlineStr">
         <is>
           <t>A. 学歴・研究</t>
         </is>
       </c>
+      <c r="B8" s="106" t="n"/>
+      <c r="C8" s="107" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="70">
       <c r="A9" s="101" t="inlineStr">
@@ -2215,12 +2222,15 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="22" customHeight="1" s="70">
       <c r="A13" s="105" t="inlineStr">
         <is>
           <t>B. キャリアの転機（朝霞工場長時代の具体的実績）</t>
         </is>
       </c>
+      <c r="B13" s="106" t="n"/>
+      <c r="C13" s="107" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="70">
       <c r="A14" s="101" t="inlineStr">
@@ -2273,7 +2283,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="55" customHeight="1" s="70">
+    <row r="17" ht="70" customHeight="1" s="70">
       <c r="A17" s="102" t="inlineStr">
         <is>
           <t>実績③：大手企業との共同開発</t>
@@ -2281,12 +2291,12 @@
       </c>
       <c r="B17" s="103" t="inlineStr">
         <is>
-          <t>すべり軸受・耐摩耗部品向けの新合金開発で大手企業と連携（社内実績として、航空機ランディングギア用銅合金メタルブッシュは世界シェア20%でトップレベル）</t>
+          <t>本田技研工業とのすべり軸受（F1エンジン用コンロッドメタル）の共同開発。ベリリウム銅代替のコルソン系銅合金「NC50合金」（高強度・高熱伝導性）を採用し、製法特許を本田技研工業と共同出願・取得。F1車に実採用された</t>
         </is>
       </c>
       <c r="C17" s="103" t="inlineStr">
         <is>
-          <t>本人インタビュー＋社内ビジョン資料との整合</t>
+          <t>本人インタビュー＋日刊鉄鋼新聞（Japan Metal Daily）報道「エンジン部品用銅合金／三芳合金が特許取得／本田技研と共同 F1車に採用」で外部裏付け済み</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2317,15 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="22" customHeight="1" s="70">
       <c r="A20" s="105" t="inlineStr">
         <is>
           <t>C. 技術者としての専門性</t>
         </is>
       </c>
+      <c r="B20" s="106" t="n"/>
+      <c r="C20" s="107" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="70">
       <c r="A21" s="101" t="inlineStr">
@@ -2366,12 +2379,15 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="22" customHeight="1" s="70">
       <c r="A25" s="105" t="inlineStr">
         <is>
           <t>D. 後継者に求める資質</t>
         </is>
       </c>
+      <c r="B25" s="106" t="n"/>
+      <c r="C25" s="107" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="70">
       <c r="A26" s="101" t="inlineStr">
@@ -2458,12 +2474,15 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1" s="70">
       <c r="A32" s="105" t="inlineStr">
         <is>
           <t>E. 企業文化・組織</t>
         </is>
       </c>
+      <c r="B32" s="106" t="n"/>
+      <c r="C32" s="107" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1" s="70">
       <c r="A33" s="101" t="inlineStr">
@@ -2499,12 +2518,15 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="22" customHeight="1" s="70">
       <c r="A36" s="105" t="inlineStr">
         <is>
           <t>F. 製品開発課の理念（採用基準として明文化すべき共感ポイント）</t>
         </is>
       </c>
+      <c r="B36" s="106" t="n"/>
+      <c r="C36" s="107" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1" s="70">
       <c r="A37" s="101" t="inlineStr">
@@ -2591,12 +2613,15 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43" ht="22" customHeight="1" s="70">
       <c r="A43" s="105" t="inlineStr">
         <is>
           <t>G. 何を成果とみなすか（評価基準・OJT設計への活用）</t>
         </is>
       </c>
+      <c r="B43" s="106" t="n"/>
+      <c r="C43" s="107" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="70">
       <c r="A44" s="101" t="inlineStr">
@@ -2666,6 +2691,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49" ht="32" customHeight="1" s="70">
       <c r="A49" s="104" t="inlineStr">
         <is>
@@ -2676,9 +2702,9 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A32:C32"/>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -2079,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="70" min="1" max="1"/>
@@ -2161,7 +2161,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="22" customHeight="1" s="70">
       <c r="A8" s="105" t="inlineStr">
         <is>
@@ -2222,7 +2221,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="22" customHeight="1" s="70">
       <c r="A13" s="105" t="inlineStr">
         <is>
@@ -2317,7 +2315,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="22" customHeight="1" s="70">
       <c r="A20" s="105" t="inlineStr">
         <is>
@@ -2379,7 +2376,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25" ht="22" customHeight="1" s="70">
       <c r="A25" s="105" t="inlineStr">
         <is>
@@ -2474,7 +2470,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="22" customHeight="1" s="70">
       <c r="A32" s="105" t="inlineStr">
         <is>
@@ -2518,7 +2513,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="22" customHeight="1" s="70">
       <c r="A36" s="105" t="inlineStr">
         <is>
@@ -2613,7 +2607,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43" ht="22" customHeight="1" s="70">
       <c r="A43" s="105" t="inlineStr">
         <is>
@@ -2691,19 +2684,95 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49" ht="32" customHeight="1" s="70">
-      <c r="A49" s="104" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="105" t="inlineStr">
+        <is>
+          <t>H. 社会人博士支援に関する示唆（将来の制度設計への提言）</t>
+        </is>
+      </c>
+      <c r="B48" s="106" t="n"/>
+      <c r="C48" s="107" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" s="70">
+      <c r="A49" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B49" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C49" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="55" customHeight="1" s="70">
+      <c r="A50" s="102" t="inlineStr">
+        <is>
+          <t>研究テーマと実務の関係</t>
+        </is>
+      </c>
+      <c r="B50" s="103" t="inlineStr">
+        <is>
+          <t>NC50合金開発と博士研究テーマ（結晶粒成長抑制）に直接の因果関係はないが、同じ銅合金分野での問題意識は共通していた</t>
+        </is>
+      </c>
+      <c r="C50" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" s="70">
+      <c r="A51" s="102" t="inlineStr">
+        <is>
+          <t>後継者へのアドバイス</t>
+        </is>
+      </c>
+      <c r="B51" s="103" t="inlineStr">
+        <is>
+          <t>仕事と研究を分けて考えず、日々の業務課題をそのまま研究テーマにするべき</t>
+        </is>
+      </c>
+      <c r="C51" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="55" customHeight="1" s="70">
+      <c r="A52" s="102" t="inlineStr">
+        <is>
+          <t>会社が最優先で支援すべきこと</t>
+        </is>
+      </c>
+      <c r="B52" s="103" t="inlineStr">
+        <is>
+          <t>業務課題を研究テーマに昇華できるような、指導教員・大学との接点づくり（金銭支援や業務調整以上に重要）</t>
+        </is>
+      </c>
+      <c r="C52" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1" s="70">
+      <c r="A53" s="104" t="inlineStr">
         <is>
           <t>【要確認事項】博士学位論文の正式タイトル・取得年度（2014年 or 2015年）は、学位記または宇都宮大学への照会で確定し、本表を更新してください。</t>
         </is>
       </c>
     </row>
+    <row r="54" ht="55" customHeight="1" s="70"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A43:C43"/>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -2079,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="70" min="1" max="1"/>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="55" customHeight="1" s="70">
+    <row r="10" ht="85" customHeight="1" s="70">
       <c r="A10" s="102" t="inlineStr">
         <is>
           <t>博士論文テーマ</t>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
-          <t>高強度・高導電性銅合金の合金設計・析出強化機構。特に「結晶粒成長をいかに抑制するか（粒界の易動度）」に注力</t>
+          <t>「析出強化型Cu-Cr-Zr系合金の耐熱性改善に関する研究」（2014年、宇都宮大学大学院工学研究科システム創成工学専攻、指導教員：高山善匡教授）。三芳合金工業在職中の2011～2013年度、社会人ドクターとして取得。Cu-Cr-Zr系銅合金にAgを0～1.2mass%添加し、900℃復元中の結晶粒成長挙動・耐熱性への影響を解明。Ag添加により析出強化量・固溶強化量が向上し、Ag濃度0.57mass%で耐熱強度23%改善、1.13mass%で約40%改善を実証</t>
         </is>
       </c>
       <c r="C10" s="103" t="inlineStr">
         <is>
-          <t>本人インタビュー。特許JP2008223069A「高強度高導電性銅合金及びその製造方法」の技術系譜と一致</t>
+          <t>学位論文本文（原本確認済み）</t>
         </is>
       </c>
     </row>
@@ -2761,17 +2761,167 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="45" customHeight="1" s="70">
-      <c r="A53" s="104" t="inlineStr">
-        <is>
-          <t>【要確認事項】博士学位論文の正式タイトル・取得年度（2014年 or 2015年）は、学位記または宇都宮大学への照会で確定し、本表を更新してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="55" customHeight="1" s="70"/>
+    <row r="53" ht="45" customHeight="1" s="70"/>
+    <row r="54" ht="22" customHeight="1" s="70">
+      <c r="A54" s="105" t="inlineStr">
+        <is>
+          <t>I. 学術研究業績（確定情報）</t>
+        </is>
+      </c>
+      <c r="B54" s="106" t="n"/>
+      <c r="C54" s="107" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1" s="70">
+      <c r="A55" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B55" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C55" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1" s="70">
+      <c r="A56" s="102" t="inlineStr">
+        <is>
+          <t>査読付き学術論文（筆頭著者・全2報）</t>
+        </is>
+      </c>
+      <c r="B56" s="103" t="inlineStr">
+        <is>
+          <t>①「Cu-Cr-Zr-Ag合金の機械的性質に及ぼす焼きなまし条件の影響」銅と銅合金 第51巻1号（2011）
+②「Cu-Cr-Zr-Ag合金の焼なまし後の機械的性質及び粒成長に及ぼすAg含有量の影響」銅と銅合金 第52巻1号（2012）
+（共著：新井真人、藤井慎太朗、高山善匡 他、製品開発課の同僚と連名）</t>
+        </is>
+      </c>
+      <c r="C56" s="103" t="inlineStr">
+        <is>
+          <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1" s="70">
+      <c r="A57" s="102" t="inlineStr">
+        <is>
+          <t>国際会議論文（筆頭著者）</t>
+        </is>
+      </c>
+      <c r="B57" s="103" t="inlineStr">
+        <is>
+          <t>"EFFECT OF Ag CONTENT ON GRAIN GROWTH DURING REVERSION IN PRECIPITATION HARDENED Cu-Cr-Zr-Ag ALLOYS" The 8th Pacific Rim International Congress on Advanced Material and Processing (PRICM8), TMS, 2013</t>
+        </is>
+      </c>
+      <c r="C57" s="103" t="inlineStr">
+        <is>
+          <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1" s="70">
+      <c r="A58" s="102" t="inlineStr">
+        <is>
+          <t>口頭発表</t>
+        </is>
+      </c>
+      <c r="B58" s="103" t="inlineStr">
+        <is>
+          <t>日本鋼学会 第51回・第52回講演大会（2011・2012年、いずれも筆頭発表者）、PRICM8国際会議（2013年、筆頭発表者）</t>
+        </is>
+      </c>
+      <c r="C58" s="103" t="inlineStr">
+        <is>
+          <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1" s="70">
+      <c r="A60" s="105" t="inlineStr">
+        <is>
+          <t>J. 企業文化としての「博士人材」の裏付け</t>
+        </is>
+      </c>
+      <c r="B60" s="106" t="n"/>
+      <c r="C60" s="107" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1" s="70">
+      <c r="A61" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B61" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C61" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="65" customHeight="1" s="70">
+      <c r="A62" s="102" t="inlineStr">
+        <is>
+          <t>経営陣も博士号取得者</t>
+        </is>
+      </c>
+      <c r="B62" s="103" t="inlineStr">
+        <is>
+          <t>大和合金株式会社の代表取締役・萩野源次郎社長も2010年度に博士号を取得。江口氏は謝辞にて「暖かい激励とアドバイスを頂いた」と記載。技術を経営層自らが体系化する文化が存在することを裏付け</t>
+        </is>
+      </c>
+      <c r="C62" s="103" t="inlineStr">
+        <is>
+          <t>学位論文謝辞</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="55" customHeight="1" s="70">
+      <c r="A63" s="102" t="inlineStr">
+        <is>
+          <t>社外の技術顧問体制</t>
+        </is>
+      </c>
+      <c r="B63" s="103" t="inlineStr">
+        <is>
+          <t>古河電気工業出身の工学博士（元研究開発部技師長）が技術顧問として長年指導。社会人ドクター取得を会社として後押しする土壌がある</t>
+        </is>
+      </c>
+      <c r="C63" s="103" t="inlineStr">
+        <is>
+          <t>学位論文謝辞</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="55" customHeight="1" s="70">
+      <c r="A64" s="102" t="inlineStr">
+        <is>
+          <t>共同研究チームの存在</t>
+        </is>
+      </c>
+      <c r="B64" s="103" t="inlineStr">
+        <is>
+          <t>製品開発課の同僚（新井真人係長、藤井慎太朗氏ほか）が実験全般を推進し、社会人ドクターの研究をチームでサポート。1人で抱え込まず組織的に取り組む文化</t>
+        </is>
+      </c>
+      <c r="C64" s="103" t="inlineStr">
+        <is>
+          <t>学位論文謝辞</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A60:C60"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
@@ -2779,6 +2929,7 @@
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="コンサルティング実施計画書（大和合金株式会社）" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="中核人材ペルソナ（案）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="後継者ペルソナ要件（案）" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'コンサルティング実施計画書（大和合金株式会社）'!$A$1:$F$23</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -250,8 +251,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -291,6 +298,21 @@
         <fgColor rgb="008EA9DB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5395"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="48">
     <border>
@@ -895,7 +917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1184,6 +1206,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2935,4 +2966,555 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="70" min="1" max="1"/>
+    <col width="14" customWidth="1" style="70" min="2" max="2"/>
+    <col width="78" customWidth="1" style="70" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="70">
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t>後継者ペルソナ要件（採用基準・案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1" s="70">
+      <c r="A2" s="100" t="inlineStr">
+        <is>
+          <t>※「中核人材ペルソナ（案）」シートの根拠情報（本人インタビュー、学位論文、製品開発課の理念資料）を統合し、求人票・面接評価票に転用できる形に要件化したもの。第2回コンサルティング（採用基準の言語化）でのたたき台。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="70">
+      <c r="A4" s="108" t="inlineStr">
+        <is>
+          <t>A. ポジション概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="70">
+      <c r="A5" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="101" t="inlineStr"/>
+      <c r="C5" s="101" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="70">
+      <c r="A6" s="102" t="inlineStr">
+        <is>
+          <t>ポジション名</t>
+        </is>
+      </c>
+      <c r="B6" s="102" t="inlineStr"/>
+      <c r="C6" s="103" t="inlineStr">
+        <is>
+          <t>製品開発課 中核技術者（将来の技術系幹部候補）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="70">
+      <c r="A7" s="102" t="inlineStr">
+        <is>
+          <t>募集背景</t>
+        </is>
+      </c>
+      <c r="B7" s="102" t="inlineStr"/>
+      <c r="C7" s="103" t="inlineStr">
+        <is>
+          <t>技術習得に10～20年を要する専門分野（特殊銅合金）において、現工場長・取締役（技術系トップ）の後継となる中核人材を、中長期的な視点で確保する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="70">
+      <c r="A9" s="108" t="inlineStr">
+        <is>
+          <t>B. MUST要件（学歴・専門性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="70">
+      <c r="A10" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B10" s="101" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C10" s="101" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="70">
+      <c r="A11" s="102" t="inlineStr">
+        <is>
+          <t>学歴</t>
+        </is>
+      </c>
+      <c r="B11" s="109" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="C11" s="103" t="inlineStr">
+        <is>
+          <t>理工系（材料工学・金属工学・機械材料系）修士以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="35" customHeight="1" s="70">
+      <c r="A12" s="102" t="inlineStr">
+        <is>
+          <t>専門分野</t>
+        </is>
+      </c>
+      <c r="B12" s="109" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="C12" s="103" t="inlineStr">
+        <is>
+          <t>非鉄金属材料（特に銅合金）に関する知識、または金属材料全般の基礎知識</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="35" customHeight="1" s="70">
+      <c r="A13" s="102" t="inlineStr">
+        <is>
+          <t>志向性</t>
+        </is>
+      </c>
+      <c r="B13" s="109" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="C13" s="103" t="inlineStr">
+        <is>
+          <t>実務課題を科学的・体系的に掘り下げることに関心がある（研究開発志向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="70">
+      <c r="A15" s="108" t="inlineStr">
+        <is>
+          <t>C. 歓迎要件</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="70">
+      <c r="A16" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B16" s="101" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C16" s="101" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="35" customHeight="1" s="70">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>学位</t>
+        </is>
+      </c>
+      <c r="B17" s="110" t="inlineStr">
+        <is>
+          <t>歓迎</t>
+        </is>
+      </c>
+      <c r="C17" s="103" t="inlineStr">
+        <is>
+          <t>博士号（工学）取得者、または社会人ドクターとして取得する意欲がある人</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1" s="70">
+      <c r="A18" s="102" t="inlineStr">
+        <is>
+          <t>研究発表経験</t>
+        </is>
+      </c>
+      <c r="B18" s="110" t="inlineStr">
+        <is>
+          <t>歓迎</t>
+        </is>
+      </c>
+      <c r="C18" s="103" t="inlineStr">
+        <is>
+          <t>学会発表・論文執筆・特許出願のいずれかの経験（ロールモデル：現工場長は査読付き論文2報・国際会議論文1報・特許共同出願を実績として保有）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1" s="70">
+      <c r="A19" s="102" t="inlineStr">
+        <is>
+          <t>対外共同研究経験</t>
+        </is>
+      </c>
+      <c r="B19" s="110" t="inlineStr">
+        <is>
+          <t>歓迎</t>
+        </is>
+      </c>
+      <c r="C19" s="103" t="inlineStr">
+        <is>
+          <t>大手企業・公的研究機関等、社外の専門家と対等に議論しながらプロジェクトを推進した経験</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="70">
+      <c r="A21" s="108" t="inlineStr">
+        <is>
+          <t>D. 人物・価値観要件（必須）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="70">
+      <c r="A22" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B22" s="101" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C22" s="101" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1" s="70">
+      <c r="A23" s="102" t="inlineStr">
+        <is>
+          <t>製品開発課バリューへの共感</t>
+        </is>
+      </c>
+      <c r="B23" s="109" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="C23" s="103" t="inlineStr">
+        <is>
+          <t>①再現性の追求（技術的エビデンス重視）　②記録の徹底　③完遂へのこだわり　の3つに共感できること</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1" s="70">
+      <c r="A24" s="102" t="inlineStr">
+        <is>
+          <t>必須資質（優先順位）</t>
+        </is>
+      </c>
+      <c r="B24" s="109" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="C24" s="103" t="inlineStr">
+        <is>
+          <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢　＞　③立場の違う相手と対等に議論できる度胸</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="35" customHeight="1" s="70">
+      <c r="A25" s="102" t="inlineStr">
+        <is>
+          <t>失敗への向き合い方</t>
+        </is>
+      </c>
+      <c r="B25" s="109" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="C25" s="103" t="inlineStr">
+        <is>
+          <t>失敗から逃げず、原因を追究できること（「任せられる」と判断する最重要ポイント）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="35" customHeight="1" s="70">
+      <c r="A26" s="102" t="inlineStr">
+        <is>
+          <t>NG基準</t>
+        </is>
+      </c>
+      <c r="B26" s="109" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="C26" s="103" t="inlineStr">
+        <is>
+          <t>都合の悪い情報を隠す、報告を遅らせる姿勢が見られる人は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" s="70">
+      <c r="A28" s="108" t="inlineStr">
+        <is>
+          <t>E. キャリアパス・育成タイムライン（イメージ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="70">
+      <c r="A29" s="101" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="B29" s="101" t="inlineStr"/>
+      <c r="C29" s="101" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1" s="70">
+      <c r="A30" s="102" t="inlineStr">
+        <is>
+          <t>入社～3年</t>
+        </is>
+      </c>
+      <c r="B30" s="102" t="inlineStr"/>
+      <c r="C30" s="103" t="inlineStr">
+        <is>
+          <t>製造・品質保証など現場配属で「モノづくりの基盤」を体得</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1" s="70">
+      <c r="A31" s="102" t="inlineStr">
+        <is>
+          <t>5～10年</t>
+        </is>
+      </c>
+      <c r="B31" s="102" t="inlineStr"/>
+      <c r="C31" s="103" t="inlineStr">
+        <is>
+          <t>複数部門（製造・品質・開発等）を経験しながら、社外との共同研究機会を通じて対外折衝力を養成</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1" s="70">
+      <c r="A32" s="102" t="inlineStr">
+        <is>
+          <t>10～20年</t>
+        </is>
+      </c>
+      <c r="B32" s="102" t="inlineStr"/>
+      <c r="C32" s="103" t="inlineStr">
+        <is>
+          <t>製品開発課の中核技術者として自立。必要に応じ社会人ドクターとして学位取得、技術の体系化・発信を担う</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" s="70">
+      <c r="A34" s="108" t="inlineStr">
+        <is>
+          <t>F. 期待する成果・評価基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="70">
+      <c r="A35" s="101" t="inlineStr">
+        <is>
+          <t>期間</t>
+        </is>
+      </c>
+      <c r="B35" s="101" t="inlineStr"/>
+      <c r="C35" s="101" t="inlineStr">
+        <is>
+          <t>成果指標</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1" s="70">
+      <c r="A36" s="102" t="inlineStr">
+        <is>
+          <t>短期（2～3ヶ月）</t>
+        </is>
+      </c>
+      <c r="B36" s="102" t="inlineStr"/>
+      <c r="C36" s="103" t="inlineStr">
+        <is>
+          <t>仮説検証の完了数（失敗して条件を否定できたことも成果としてカウント）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="35" customHeight="1" s="70">
+      <c r="A37" s="102" t="inlineStr">
+        <is>
+          <t>中期（半年～1年）</t>
+        </is>
+      </c>
+      <c r="B37" s="102" t="inlineStr"/>
+      <c r="C37" s="103" t="inlineStr">
+        <is>
+          <t>新価値の「型」の市場投入数（スペック承認・特許出願・ノウハウ登録等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="35" customHeight="1" s="70">
+      <c r="A38" s="102" t="inlineStr">
+        <is>
+          <t>長期（3年～）</t>
+        </is>
+      </c>
+      <c r="B38" s="102" t="inlineStr"/>
+      <c r="C38" s="103" t="inlineStr">
+        <is>
+          <t>競争優位のポートフォリオへの貢献（開発テーマが継続的に動いている状態の維持）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" s="70">
+      <c r="A40" s="108" t="inlineStr">
+        <is>
+          <t>G. 面接評価チェック項目（行動特性ベース質問例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="70">
+      <c r="A41" s="101" t="inlineStr">
+        <is>
+          <t>確認したい資質</t>
+        </is>
+      </c>
+      <c r="B41" s="101" t="inlineStr"/>
+      <c r="C41" s="101" t="inlineStr">
+        <is>
+          <t>質問例</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1" s="70">
+      <c r="A42" s="102" t="inlineStr">
+        <is>
+          <t>失敗への向き合い方</t>
+        </is>
+      </c>
+      <c r="B42" s="102" t="inlineStr"/>
+      <c r="C42" s="103" t="inlineStr">
+        <is>
+          <t>「過去の失敗で、原因を最後まで追究した経験を教えてください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="35" customHeight="1" s="70">
+      <c r="A43" s="102" t="inlineStr">
+        <is>
+          <t>現場主義</t>
+        </is>
+      </c>
+      <c r="B43" s="102" t="inlineStr"/>
+      <c r="C43" s="103" t="inlineStr">
+        <is>
+          <t>「データや報告だけでなく、自分の目で現場を確かめに行った経験はありますか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1" s="70">
+      <c r="A44" s="102" t="inlineStr">
+        <is>
+          <t>対話力・度胸</t>
+        </is>
+      </c>
+      <c r="B44" s="102" t="inlineStr"/>
+      <c r="C44" s="103" t="inlineStr">
+        <is>
+          <t>「専門分野の異なる相手（他社・研究機関等）と議論し、意見が対立した経験はありますか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1" s="70">
+      <c r="A45" s="102" t="inlineStr">
+        <is>
+          <t>記録・完遂への姿勢</t>
+        </is>
+      </c>
+      <c r="B45" s="102" t="inlineStr"/>
+      <c r="C45" s="103" t="inlineStr">
+        <is>
+          <t>「途中で頓挫しそうになったタスクを、最後までやり切った経験を教えてください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="35" customHeight="1" s="70">
+      <c r="A46" s="102" t="inlineStr">
+        <is>
+          <t>誠実性（NG基準の裏取り）</t>
+        </is>
+      </c>
+      <c r="B46" s="102" t="inlineStr"/>
+      <c r="C46" s="103" t="inlineStr">
+        <is>
+          <t>「都合の悪い報告を、誰にどのタイミングで伝えましたか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1" s="70">
+      <c r="A48" s="108" t="inlineStr">
+        <is>
+          <t>H. ロールモデル要約（現・取締役 本社工場長のキャリア）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="70" customHeight="1" s="70">
+      <c r="A49" s="103" t="inlineStr">
+        <is>
+          <t>製造→品質保証→製造→製品開発課→朝霞工場長→取締役本社工場長。修士卒で入社後、在籍しながら社会人ドクターとして宇都宮大学で博士号（工学）を取得（2014年）。ITER（核融合炉）向け銅合金の国家研究機関との共同開発、本田技研工業とのF1エンジン用コンロッドメタル共同開発・特許共同出願など、現場経験を土台に外部と対等に渡り合う技術者として成長した実例。詳細は「中核人材ペルソナ（案）」シートを参照。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -9,6 +9,7 @@
     <sheet name="コンサルティング実施計画書（大和合金株式会社）" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="中核人材ペルソナ（案）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="後継者ペルソナ要件（案）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="オンラインセミナー講師一覧" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'コンサルティング実施計画書（大和合金株式会社）'!$A$1:$F$23</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="35">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -257,6 +258,21 @@
       <color rgb="00C00000"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -917,7 +933,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1214,6 +1230,27 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3002,6 +3039,8 @@
           <t>A. ポジション概要</t>
         </is>
       </c>
+      <c r="B4" s="106" t="n"/>
+      <c r="C4" s="107" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="70">
       <c r="A5" s="101" t="inlineStr">
@@ -3048,6 +3087,8 @@
           <t>B. MUST要件（学歴・専門性）</t>
         </is>
       </c>
+      <c r="B9" s="106" t="n"/>
+      <c r="C9" s="107" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="70">
       <c r="A10" s="101" t="inlineStr">
@@ -3123,6 +3164,8 @@
           <t>C. 歓迎要件</t>
         </is>
       </c>
+      <c r="B15" s="106" t="n"/>
+      <c r="C15" s="107" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="70">
       <c r="A16" s="101" t="inlineStr">
@@ -3198,6 +3241,8 @@
           <t>D. 人物・価値観要件（必須）</t>
         </is>
       </c>
+      <c r="B21" s="106" t="n"/>
+      <c r="C21" s="107" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="70">
       <c r="A22" s="101" t="inlineStr">
@@ -3290,6 +3335,8 @@
           <t>E. キャリアパス・育成タイムライン（イメージ）</t>
         </is>
       </c>
+      <c r="B28" s="106" t="n"/>
+      <c r="C28" s="107" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="70">
       <c r="A29" s="101" t="inlineStr">
@@ -3349,6 +3396,8 @@
           <t>F. 期待する成果・評価基準</t>
         </is>
       </c>
+      <c r="B34" s="106" t="n"/>
+      <c r="C34" s="107" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="70">
       <c r="A35" s="101" t="inlineStr">
@@ -3408,6 +3457,8 @@
           <t>G. 面接評価チェック項目（行動特性ベース質問例）</t>
         </is>
       </c>
+      <c r="B40" s="106" t="n"/>
+      <c r="C40" s="107" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="70">
       <c r="A41" s="101" t="inlineStr">
@@ -3493,6 +3544,8 @@
           <t>H. ロールモデル要約（現・取締役 本社工場長のキャリア）</t>
         </is>
       </c>
+      <c r="B48" s="106" t="n"/>
+      <c r="C48" s="107" t="n"/>
     </row>
     <row r="49" ht="70" customHeight="1" s="70">
       <c r="A49" s="103" t="inlineStr">
@@ -3500,6 +3553,8 @@
           <t>製造→品質保証→製造→製品開発課→朝霞工場長→取締役本社工場長。修士卒で入社後、在籍しながら社会人ドクターとして宇都宮大学で博士号（工学）を取得（2014年）。ITER（核融合炉）向け銅合金の国家研究機関との共同開発、本田技研工業とのF1エンジン用コンロッドメタル共同開発・特許共同出願など、現場経験を土台に外部と対等に渡り合う技術者として成長した実例。詳細は「中核人材ペルソナ（案）」シートを参照。</t>
         </is>
       </c>
+      <c r="B49" s="106" t="n"/>
+      <c r="C49" s="107" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3517,4 +3572,290 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="70" min="1" max="1"/>
+    <col width="16" customWidth="1" style="70" min="2" max="2"/>
+    <col width="12" customWidth="1" style="70" min="3" max="3"/>
+    <col width="26" customWidth="1" style="70" min="4" max="4"/>
+    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+    <col width="55" customWidth="1" style="70" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="70">
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t>「人材確保ノウハウ集中支援事業」オンラインセミナー講師一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="70">
+      <c r="A2" s="111" t="inlineStr">
+        <is>
+          <t>※共通シリーズ名「売上100億円を目指す中小企業経営者のための人材戦略」。各講師のPDFシラバス（アップロードされた第2・3・4・6・7・8回分）をもとに要約。第1回・第5回のシラバスは未取得。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="70">
+      <c r="A4" s="101" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="B4" s="101" t="inlineStr">
+        <is>
+          <t>日程</t>
+        </is>
+      </c>
+      <c r="C4" s="101" t="inlineStr">
+        <is>
+          <t>講師名</t>
+        </is>
+      </c>
+      <c r="D4" s="101" t="inlineStr">
+        <is>
+          <t>所属・肩書</t>
+        </is>
+      </c>
+      <c r="E4" s="101" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="F4" s="101" t="inlineStr">
+        <is>
+          <t>概要・ポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="95" customHeight="1" s="70">
+      <c r="A5" s="112" t="inlineStr">
+        <is>
+          <t>第2回</t>
+        </is>
+      </c>
+      <c r="B5" s="112" t="inlineStr">
+        <is>
+          <t>2月12日(木)
+14:00~15:20</t>
+        </is>
+      </c>
+      <c r="C5" s="113" t="inlineStr">
+        <is>
+          <t>大久保 圭祐</t>
+        </is>
+      </c>
+      <c r="D5" s="114" t="inlineStr">
+        <is>
+          <t>合同会社tri
+代表CEO</t>
+        </is>
+      </c>
+      <c r="E5" s="114" t="inlineStr">
+        <is>
+          <t>離職対策は採用前に始まる―候補者評価～入社後90日間を一貫設計"令和版オンボーディング"</t>
+        </is>
+      </c>
+      <c r="F5" s="114" t="inlineStr">
+        <is>
+          <t>採用前の「候補者評価」から入社後90日間の関わり方までを一連の流れとして設計。人事専任がいない中小企業でも実装できる定着施策が主眼。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="95" customHeight="1" s="70">
+      <c r="A6" s="112" t="inlineStr">
+        <is>
+          <t>第3回</t>
+        </is>
+      </c>
+      <c r="B6" s="112" t="inlineStr">
+        <is>
+          <t>2月19日(木)
+14:00~15:20</t>
+        </is>
+      </c>
+      <c r="C6" s="113" t="inlineStr">
+        <is>
+          <t>堺 孝善</t>
+        </is>
+      </c>
+      <c r="D6" s="114" t="inlineStr">
+        <is>
+          <t>(記載なし)</t>
+        </is>
+      </c>
+      <c r="E6" s="114" t="inlineStr">
+        <is>
+          <t>欲しい人材を徹底的に考える―いま求められる採用設計
+～人数合わせから脱却する、量×質に基づく人材獲得計画～</t>
+        </is>
+      </c>
+      <c r="F6" s="114" t="inlineStr">
+        <is>
+          <t>採用を「手法」ではなく経営戦略と連動した「設計」の問題として捉え直す。人数（量）だけでなく事業フェーズに応じた「質」を含めた人材要件の整理を解説。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="95" customHeight="1" s="70">
+      <c r="A7" s="112" t="inlineStr">
+        <is>
+          <t>第4回</t>
+        </is>
+      </c>
+      <c r="B7" s="112" t="inlineStr">
+        <is>
+          <t>2月26日(木)
+14:00~15:20</t>
+        </is>
+      </c>
+      <c r="C7" s="113" t="inlineStr">
+        <is>
+          <t>永見 昌彦</t>
+        </is>
+      </c>
+      <c r="D7" s="114" t="inlineStr">
+        <is>
+          <t>アルドーニ株式会社
+代表取締役</t>
+        </is>
+      </c>
+      <c r="E7" s="114" t="inlineStr">
+        <is>
+          <t>売上100億円をめざす中小企業のための、失敗しない「人事評価制度」導入・運用の全ステップ</t>
+        </is>
+      </c>
+      <c r="F7" s="114" t="inlineStr">
+        <is>
+          <t>MBO・コンピテンシー評価・OKR等の型を比較し、導入5ステップと運用（評価者教育・フィードバック）、評価の報酬反映までを実務的に解説。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="95" customHeight="1" s="70">
+      <c r="A8" s="115" t="inlineStr">
+        <is>
+          <t>第6回</t>
+        </is>
+      </c>
+      <c r="B8" s="115" t="inlineStr">
+        <is>
+          <t>6月23日(火)
+14:00~15:20</t>
+        </is>
+      </c>
+      <c r="C8" s="116" t="inlineStr">
+        <is>
+          <t>猿渡 秀樹</t>
+        </is>
+      </c>
+      <c r="D8" s="117" t="inlineStr">
+        <is>
+          <t>合同会社HumanRelations
+代表CEO</t>
+        </is>
+      </c>
+      <c r="E8" s="117" t="inlineStr">
+        <is>
+          <t>売上100億円を目指す中小企業経営者のための人材戦略
+AI活用で強くする採用力と定着力</t>
+        </is>
+      </c>
+      <c r="F8" s="117" t="inlineStr">
+        <is>
+          <t>採用広報・採用基準・評価制度・教育目標・給与還元の「5軸連動（ペンタゴンモデル）」を提唱。AIで現場のリアルな一次情報を求人票に反映し、90日オンボーディングまで一気通貫で設計。
+※本コンサルティングの担当講師。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="95" customHeight="1" s="70">
+      <c r="A9" s="112" t="inlineStr">
+        <is>
+          <t>第7回</t>
+        </is>
+      </c>
+      <c r="B9" s="112" t="inlineStr">
+        <is>
+          <t>7月1日(水)
+14:00~15:20</t>
+        </is>
+      </c>
+      <c r="C9" s="113" t="inlineStr">
+        <is>
+          <t>中山 健児</t>
+        </is>
+      </c>
+      <c r="D9" s="114" t="inlineStr">
+        <is>
+          <t>株式会社シリンクス
+代表取締役</t>
+        </is>
+      </c>
+      <c r="E9" s="114" t="inlineStr">
+        <is>
+          <t>将来を見据えた人事制度で人材定着を実現</t>
+        </is>
+      </c>
+      <c r="F9" s="114" t="inlineStr">
+        <is>
+          <t>「魅せる処遇」3つのポイント（報酬の可視化・期待の明確化・成長の環境整備）を軸に、IT・サービス業・技術職の3実践事例で人事制度刷新を解説。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="95" customHeight="1" s="70">
+      <c r="A10" s="112" t="inlineStr">
+        <is>
+          <t>第8回</t>
+        </is>
+      </c>
+      <c r="B10" s="112" t="inlineStr">
+        <is>
+          <t>7月8日(水)
+14:00~15:20</t>
+        </is>
+      </c>
+      <c r="C10" s="113" t="inlineStr">
+        <is>
+          <t>武田 学</t>
+        </is>
+      </c>
+      <c r="D10" s="114" t="inlineStr">
+        <is>
+          <t>G&amp;カンパニー株式会社
+代表取締役</t>
+        </is>
+      </c>
+      <c r="E10" s="114" t="inlineStr">
+        <is>
+          <t>理念×採用でブレない採用の仕組みづくり</t>
+        </is>
+      </c>
+      <c r="F10" s="114" t="inlineStr">
+        <is>
+          <t>経営者と採用担当者が「一心同体」であることの重要性。理念（MVV）を掲げるだけでなく、採用担当者が経営者と同じ熱量で語れる体制づくりと、採用を経営直結のプロジェクトマネジメントとして扱う視点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1" s="70">
+      <c r="A12" s="111" t="inlineStr">
+        <is>
+          <t>【傾向】6名に共通するのは「採用だけを切り離さず、評価・処遇・オンボーディングまで一気通貫で設計する」という思想。特に猿渡氏の「5軸連動」と大久保氏の「令和版オンボーディング」は概念的重なりが大きく、武田氏の「理念×採用」は本計画書にある経営理念への共感というテーマとも接続できる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -10,6 +10,7 @@
     <sheet name="中核人材ペルソナ（案）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="後継者ペルソナ要件（案）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="オンラインセミナー講師一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="人材確保の要点（まとめ）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'コンサルティング実施計画書（大和合金株式会社）'!$A$1:$F$23</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -273,6 +274,17 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="004472C4"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -933,7 +945,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1250,6 +1262,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="10" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3858,4 +3879,210 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="70" min="1" max="1"/>
+    <col width="26" customWidth="1" style="70" min="2" max="2"/>
+    <col width="55" customWidth="1" style="70" min="3" max="3"/>
+    <col width="45" customWidth="1" style="70" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="70">
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t>人材確保の要点（まとめ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1" s="70">
+      <c r="A2" s="111" t="inlineStr">
+        <is>
+          <t>※コンサルティング実施計画書、後継者ペルソナ構築の一連の作業、オンラインセミナー講師6名のシラバスを俯瞰して整理した要点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="70">
+      <c r="A4" s="101" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="101" t="inlineStr">
+        <is>
+          <t>要点</t>
+        </is>
+      </c>
+      <c r="C4" s="101" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D4" s="101" t="inlineStr">
+        <is>
+          <t>根拠・関連資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1" s="70">
+      <c r="A5" s="118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="119" t="inlineStr">
+        <is>
+          <t>採用・評価・処遇・定着を
+一気通貫で設計する</t>
+        </is>
+      </c>
+      <c r="C5" s="114" t="inlineStr">
+        <is>
+          <t>採用単体の施策ではなく、入口（求人）から出口（評価・処遇）までを線でつなぐ。施策が「点」でバラバラなことが早期離職・採用ミスマッチの根本原因。</t>
+        </is>
+      </c>
+      <c r="D5" s="114" t="inlineStr">
+        <is>
+          <t>猿渡氏「5軸連動（ペンタゴンモデル）」／大久保氏「令和版オンボーディング」／永見氏の評価・報酬設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1" s="70">
+      <c r="A6" s="118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="119" t="inlineStr">
+        <is>
+          <t>「どんな人材が欲しいか」の
+言語化が全ての起点</t>
+        </is>
+      </c>
+      <c r="C6" s="114" t="inlineStr">
+        <is>
+          <t>感覚頼みの採用基準では誰が面接しても同じ判断ができない。人材要件（ペルソナ）を具体的に明文化することが最初のステップ。</t>
+        </is>
+      </c>
+      <c r="D6" s="114" t="inlineStr">
+        <is>
+          <t>堺氏「量×質で考える採用設計」／猿渡氏「評価基準の言語化」／「後継者ペルソナ要件（案）」シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1" s="70">
+      <c r="A7" s="118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="119" t="inlineStr">
+        <is>
+          <t>経営者自身が採用に
+コミットする</t>
+        </is>
+      </c>
+      <c r="C7" s="114" t="inlineStr">
+        <is>
+          <t>理念を掲げるだけでなく、経営者が採用担当者と同じ熱量で語れる状態を作ることが、紹介採用への依存を脱する第一歩。専任人事不在の中小企業ほど重要。</t>
+        </is>
+      </c>
+      <c r="D7" s="114" t="inlineStr">
+        <is>
+          <t>武田氏「経営者と採用担当者は一心同体」／大和合金様の課題（総務兼務・専任人事不在）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1" s="70">
+      <c r="A8" s="118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="119" t="inlineStr">
+        <is>
+          <t>「出口」の設計が
+最強の採用ブランディングになる</t>
+        </is>
+      </c>
+      <c r="C8" s="114" t="inlineStr">
+        <is>
+          <t>評価・報酬・成長機会が明確な会社ほど採用力が強い。人材確保は「採る技術」ではなく「活かす仕組み」であり、採用設計の段階からセットで作る必要がある。</t>
+        </is>
+      </c>
+      <c r="D8" s="114" t="inlineStr">
+        <is>
+          <t>永見氏「評価制度」／猿渡氏「出口が最強の採用ブランディング」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1" s="70">
+      <c r="A9" s="118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="119" t="inlineStr">
+        <is>
+          <t>中核人材（暗黙知）は
+逆算で育てる時間軸が必要</t>
+        </is>
+      </c>
+      <c r="C9" s="114" t="inlineStr">
+        <is>
+          <t>10～20年かけて培われる技術・判断力は採用した瞬間には手に入らない。育成タイムラインをあらかじめ設計し、対外共同研究や複数部門経験など成長機会を意図的に組み込む。</t>
+        </is>
+      </c>
+      <c r="D9" s="114" t="inlineStr">
+        <is>
+          <t>「中核人材ペルソナ（案）」シート（江口氏のキャリアパス・育成タイムライン）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1" s="70">
+      <c r="A10" s="118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="119" t="inlineStr">
+        <is>
+          <t>属人的な暗黙知を
+「型」に変換する</t>
+        </is>
+      </c>
+      <c r="C10" s="114" t="inlineStr">
+        <is>
+          <t>個人の勘や経験を組織の標準・評価基準として言語化しておくことで、誰が採用・育成を担当しても一定水準を保てる。人が入れ替わっても機能する体制づくりの核心。</t>
+        </is>
+      </c>
+      <c r="D10" s="114" t="inlineStr">
+        <is>
+          <t>製品開発課バリュー（再現性の追求・記録の徹底）／「何を成果とみなすか」資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" s="70">
+      <c r="A12" s="120" t="inlineStr">
+        <is>
+          <t>【総括】「欲しい人材の言語化」→「経営者主導での接点づくり」→「評価・処遇までの一気通貫設計」→「育成の時間軸設計」→「暗黙知の型化」という5段階が、人材確保の骨格となる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -2168,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="70" min="1" max="1"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1" s="70">
+    <row r="5" ht="45" customHeight="1" s="70">
       <c r="A5" s="102" t="inlineStr">
         <is>
           <t>キャリアパス</t>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B5" s="103" t="inlineStr">
         <is>
-          <t>製造 → 品質保証 → 製造 → 製品開発課 → 朝霞工場長 → 取締役 本社工場長</t>
+          <t>製造（溶解係） → 品質保証（検査） → 製造（砂型鋳造係） → 製品開発課 → 朝霞工場長 → 取締役 本社工場長</t>
         </is>
       </c>
       <c r="C5" s="103" t="inlineStr">
@@ -2233,379 +2233,408 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1" s="70">
+    <row r="6" ht="55" customHeight="1" s="70">
       <c r="A6" s="102" t="inlineStr">
         <is>
-          <t>入社時の学歴</t>
+          <t>溶解係での経験</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>修士卒で入社。その後、在籍しながら社会人学生として博士号（宇都宮大学）を取得</t>
+          <t>原料・合金要素の性質への感覚的理解が最も活き、次いで溶解温度・成分調整の勘、異常の兆候を先取りする感覚の原点もここで培われた（本人の優先順位付けによる）</t>
         </is>
       </c>
       <c r="C6" s="103" t="inlineStr">
         <is>
-          <t>本人申告</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" s="70">
-      <c r="A8" s="105" t="inlineStr">
-        <is>
-          <t>A. 学歴・研究</t>
-        </is>
-      </c>
-      <c r="B8" s="106" t="n"/>
-      <c r="C8" s="107" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="70">
-      <c r="A9" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B9" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C9" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1" s="70">
+      <c r="A7" s="102" t="inlineStr">
+        <is>
+          <t>品質保証（検査）での経験</t>
+        </is>
+      </c>
+      <c r="B7" s="103" t="inlineStr">
+        <is>
+          <t>主に検査を担当。原子吸光分析によるインゴットの化学成分分析、機械的性質（引張・硬さ）検査、導電率検査を実施。特に機械的性質検査で組織と強度のバラつきに日々直面したことが、博士研究（結晶粒成長抑制・機械的性質）への問題意識に直結</t>
+        </is>
+      </c>
+      <c r="C7" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1" s="70">
+      <c r="A8" s="102" t="inlineStr">
+        <is>
+          <t>砂型鋳造係での経験</t>
+        </is>
+      </c>
+      <c r="B8" s="103" t="inlineStr">
+        <is>
+          <t>冷却速度・凝固過程と組織（結晶粒）の関係を感覚的に理解（博士研究テーマの現場的原体験）。鋳型作りから溶解・鋳造、仕上、出荷までが一貫して完結する工程であり、納期を守ることの大切さを学んだ</t>
+        </is>
+      </c>
+      <c r="C8" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1" s="70">
+      <c r="A9" s="102" t="inlineStr">
+        <is>
+          <t>部門横断経験の意味</t>
+        </is>
+      </c>
+      <c r="B9" s="103" t="inlineStr">
+        <is>
+          <t>溶解係→品質保証→砂型鋳造係と複数部門を経験したことで、各部門が見ている指標・価値基準の違いを実感できたことに最も意味があった。後継者が理解できているかは、「自部門の都合だけでなく、前工程・後工程への影響を自然に口にするか」で見極められる</t>
+        </is>
+      </c>
+      <c r="C9" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="10" ht="85" customHeight="1" s="70">
       <c r="A10" s="102" t="inlineStr">
         <is>
+          <t>入社時の学歴</t>
+        </is>
+      </c>
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>修士卒で入社。その後、在籍しながら社会人学生として博士号（宇都宮大学）を取得</t>
+        </is>
+      </c>
+      <c r="C10" s="103" t="inlineStr">
+        <is>
+          <t>本人申告</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1" s="70"/>
+    <row r="12" ht="22" customHeight="1" s="70">
+      <c r="A12" s="105" t="inlineStr">
+        <is>
+          <t>A. 学歴・研究</t>
+        </is>
+      </c>
+      <c r="B12" s="106" t="n"/>
+      <c r="C12" s="107" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="70">
+      <c r="A13" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B13" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C13" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="70">
+      <c r="A14" s="102" t="inlineStr">
+        <is>
           <t>博士論文テーマ</t>
         </is>
       </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="B14" s="103" t="inlineStr">
         <is>
           <t>「析出強化型Cu-Cr-Zr系合金の耐熱性改善に関する研究」（2014年、宇都宮大学大学院工学研究科システム創成工学専攻、指導教員：高山善匡教授）。三芳合金工業在職中の2011～2013年度、社会人ドクターとして取得。Cu-Cr-Zr系銅合金にAgを0～1.2mass%添加し、900℃復元中の結晶粒成長挙動・耐熱性への影響を解明。Ag添加により析出強化量・固溶強化量が向上し、Ag濃度0.57mass%で耐熱強度23%改善、1.13mass%で約40%改善を実証</t>
         </is>
       </c>
-      <c r="C10" s="103" t="inlineStr">
+      <c r="C14" s="103" t="inlineStr">
         <is>
           <t>学位論文本文（原本確認済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1" s="70">
-      <c r="A11" s="102" t="inlineStr">
-        <is>
-          <t>進学の経緯／在学形態</t>
-        </is>
-      </c>
-      <c r="B11" s="103" t="inlineStr">
-        <is>
-          <t>社長の人脈による縁、かつ宇都宮大学で非鉄金属の研究が行われていたことが理由。会社に在籍しながら社会人学生として取得（休職・離職なし）</t>
-        </is>
-      </c>
-      <c r="C11" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" s="70">
-      <c r="A13" s="105" t="inlineStr">
-        <is>
-          <t>B. キャリアの転機（朝霞工場長時代の具体的実績）</t>
-        </is>
-      </c>
-      <c r="B13" s="106" t="n"/>
-      <c r="C13" s="107" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" s="70">
-      <c r="A14" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B14" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C14" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="15" ht="65" customHeight="1" s="70">
       <c r="A15" s="102" t="inlineStr">
         <is>
+          <t>進学の経緯／在学形態</t>
+        </is>
+      </c>
+      <c r="B15" s="103" t="inlineStr">
+        <is>
+          <t>社長の人脈による縁、かつ宇都宮大学で非鉄金属の研究が行われていたことが理由。会社に在籍しながら社会人学生として取得（休職・離職なし）</t>
+        </is>
+      </c>
+      <c r="C15" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1" s="70"/>
+    <row r="17" ht="22" customHeight="1" s="70">
+      <c r="A17" s="105" t="inlineStr">
+        <is>
+          <t>B. キャリアの転機（朝霞工場長時代の具体的実績）</t>
+        </is>
+      </c>
+      <c r="B17" s="106" t="n"/>
+      <c r="C17" s="107" t="n"/>
+    </row>
+    <row r="18" ht="50" customHeight="1" s="70">
+      <c r="A18" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B18" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C18" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="102" t="inlineStr">
+        <is>
           <t>実績①：現場改革</t>
         </is>
       </c>
-      <c r="B15" s="103" t="inlineStr">
+      <c r="B19" s="103" t="inlineStr">
         <is>
           <t>朝霞工場で2S活動・生産性改善を主導。現場の意識改革（毎日の2Sを習慣化する文化づくり）により、過去最高の出荷重量を「当たり前」に出せる体制を実現。最大の苦労は短期的な生産優先との時間配分バランス</t>
         </is>
       </c>
-      <c r="C15" s="103" t="inlineStr">
+      <c r="C19" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1" s="70">
-      <c r="A16" s="102" t="inlineStr">
+    <row r="20" ht="65" customHeight="1" s="70">
+      <c r="A20" s="102" t="inlineStr">
         <is>
           <t>実績②：国家プロジェクト級の共同開発</t>
         </is>
       </c>
-      <c r="B16" s="103" t="inlineStr">
+      <c r="B20" s="103" t="inlineStr">
         <is>
           <t>核融合炉（ITER＝国際熱核融合実験炉）向け銅合金の開発で、国の研究機関の研究員と対等に議論しながら新製品化。同分野で大和合金グループは世界供給量No.1の実績を保有</t>
         </is>
       </c>
-      <c r="C16" s="103" t="inlineStr">
+      <c r="C20" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー＋社内ビジョン資料（製品開発課のビジョン：ITER採用実績）との一致</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1" s="70">
-      <c r="A17" s="102" t="inlineStr">
+    <row r="21" ht="20" customHeight="1" s="70">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>実績③：大手企業との共同開発</t>
         </is>
       </c>
-      <c r="B17" s="103" t="inlineStr">
+      <c r="B21" s="103" t="inlineStr">
         <is>
           <t>本田技研工業とのすべり軸受（F1エンジン用コンロッドメタル）の共同開発。ベリリウム銅代替のコルソン系銅合金「NC50合金」（高強度・高熱伝導性）を採用し、製法特許を本田技研工業と共同出願・取得。F1車に実採用された</t>
         </is>
       </c>
-      <c r="C17" s="103" t="inlineStr">
+      <c r="C21" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー＋日刊鉄鋼新聞（Japan Metal Daily）報道「エンジン部品用銅合金／三芳合金が特許取得／本田技研と共同 F1車に採用」で外部裏付け済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="50" customHeight="1" s="70">
-      <c r="A18" s="102" t="inlineStr">
-        <is>
-          <t>ターニングポイントの本質</t>
-        </is>
-      </c>
-      <c r="B18" s="103" t="inlineStr">
-        <is>
-          <t>大手企業・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただしそれは、現場のモノづくりを広く経験した基盤があってこそ</t>
-        </is>
-      </c>
-      <c r="C18" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" s="70">
-      <c r="A20" s="105" t="inlineStr">
-        <is>
-          <t>C. 技術者としての専門性</t>
-        </is>
-      </c>
-      <c r="B20" s="106" t="n"/>
-      <c r="C20" s="107" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" s="70">
-      <c r="A21" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B21" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C21" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="22" ht="55" customHeight="1" s="70">
       <c r="A22" s="102" t="inlineStr">
         <is>
+          <t>ターニングポイントの本質</t>
+        </is>
+      </c>
+      <c r="B22" s="103" t="inlineStr">
+        <is>
+          <t>大手企業・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただしそれは、現場のモノづくりを広く経験した基盤があってこそ</t>
+        </is>
+      </c>
+      <c r="C22" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1" s="70"/>
+    <row r="24" ht="22" customHeight="1" s="70">
+      <c r="A24" s="105" t="inlineStr">
+        <is>
+          <t>C. 技術者としての専門性</t>
+        </is>
+      </c>
+      <c r="B24" s="106" t="n"/>
+      <c r="C24" s="107" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="70">
+      <c r="A25" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B25" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C25" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="70">
+      <c r="A26" s="102" t="inlineStr">
+        <is>
           <t>現在の強み</t>
         </is>
       </c>
-      <c r="B22" s="103" t="inlineStr">
+      <c r="B26" s="103" t="inlineStr">
         <is>
           <t>① 製造・品質・開発の全部門を俯瞰した技術判断力
 ② 外部（大手企業・国の研究機関）と対等に議論できる専門性・発信力</t>
         </is>
       </c>
-      <c r="C22" s="103" t="inlineStr">
+      <c r="C26" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1" s="70">
-      <c r="A23" s="102" t="inlineStr">
-        <is>
-          <t>暗黙知・勘所</t>
-        </is>
-      </c>
-      <c r="B23" s="103" t="inlineStr">
-        <is>
-          <t>不良・異常の兆候を先取りして見抜く力（10～20年かけて培われる現場感覚）</t>
-        </is>
-      </c>
-      <c r="C23" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" s="70">
-      <c r="A25" s="105" t="inlineStr">
-        <is>
-          <t>D. 後継者に求める資質</t>
-        </is>
-      </c>
-      <c r="B25" s="106" t="n"/>
-      <c r="C25" s="107" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1" s="70">
-      <c r="A26" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B26" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C26" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="27" ht="55" customHeight="1" s="70">
       <c r="A27" s="102" t="inlineStr">
         <is>
+          <t>暗黙知・勘所</t>
+        </is>
+      </c>
+      <c r="B27" s="103" t="inlineStr">
+        <is>
+          <t>不良・異常の兆候を先取りして見抜く力（10～20年かけて培われる現場感覚）</t>
+        </is>
+      </c>
+      <c r="C27" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1" s="70"/>
+    <row r="29" ht="22" customHeight="1" s="70">
+      <c r="A29" s="105" t="inlineStr">
+        <is>
+          <t>D. 後継者に求める資質</t>
+        </is>
+      </c>
+      <c r="B29" s="106" t="n"/>
+      <c r="C29" s="107" t="n"/>
+    </row>
+    <row r="30" ht="40" customHeight="1" s="70">
+      <c r="A30" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B30" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C30" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="102" t="inlineStr">
+        <is>
           <t>必須の資質（優先順位順）</t>
         </is>
       </c>
-      <c r="B27" s="103" t="inlineStr">
+      <c r="B31" s="103" t="inlineStr">
         <is>
           <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢（現場主義）　＞　③立場の違う人と対等に議論できる度胸</t>
         </is>
       </c>
-      <c r="C27" s="103" t="inlineStr">
+      <c r="C31" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="40" customHeight="1" s="70">
-      <c r="A28" s="102" t="inlineStr">
+    <row r="32" ht="40" customHeight="1" s="70">
+      <c r="A32" s="102" t="inlineStr">
         <is>
           <t>「任せられる」と判断する決め手</t>
         </is>
       </c>
-      <c r="B28" s="103" t="inlineStr">
+      <c r="B32" s="103" t="inlineStr">
         <is>
           <t>失敗への向き合い方（逃げずに原因を追究できるか）</t>
         </is>
       </c>
-      <c r="C28" s="103" t="inlineStr">
+      <c r="C32" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="40" customHeight="1" s="70">
-      <c r="A29" s="102" t="inlineStr">
+    <row r="33" ht="20" customHeight="1" s="70">
+      <c r="A33" s="102" t="inlineStr">
         <is>
           <t>NG条件</t>
         </is>
       </c>
-      <c r="B29" s="103" t="inlineStr">
+      <c r="B33" s="103" t="inlineStr">
         <is>
           <t>都合の悪い情報を隠す・報告を遅らせる姿勢</t>
         </is>
       </c>
-      <c r="C29" s="103" t="inlineStr">
+      <c r="C33" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="40" customHeight="1" s="70">
-      <c r="A30" s="102" t="inlineStr">
-        <is>
-          <t>有効だった育成環境</t>
-        </is>
-      </c>
-      <c r="B30" s="103" t="inlineStr">
-        <is>
-          <t>外部の研究者・他社との共同開発の機会を与えられたこと</t>
-        </is>
-      </c>
-      <c r="C30" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1" s="70">
-      <c r="A32" s="105" t="inlineStr">
-        <is>
-          <t>E. 企業文化・組織</t>
-        </is>
-      </c>
-      <c r="B32" s="106" t="n"/>
-      <c r="C32" s="107" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1" s="70">
-      <c r="A33" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B33" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C33" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1" s="70">
       <c r="A34" s="102" t="inlineStr">
         <is>
-          <t>大和合金ならではの文化</t>
+          <t>有効だった育成環境</t>
         </is>
       </c>
       <c r="B34" s="103" t="inlineStr">
         <is>
-          <t>「モノづくりと同じくらいヒトづくり」を本気で重視する社風</t>
+          <t>外部の研究者・他社との共同開発の機会を与えられたこと</t>
         </is>
       </c>
       <c r="C34" s="103" t="inlineStr">
         <is>
-          <t>本人インタビュー／社外公開情報とも一致</t>
+          <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" s="70">
       <c r="A36" s="105" t="inlineStr">
         <is>
-          <t>F. 製品開発課の理念（採用基準として明文化すべき共感ポイント）</t>
+          <t>E. 企業文化・組織</t>
         </is>
       </c>
       <c r="B36" s="106" t="n"/>
@@ -2631,396 +2660,443 @@
     <row r="38" ht="40" customHeight="1" s="70">
       <c r="A38" s="102" t="inlineStr">
         <is>
+          <t>大和合金ならではの文化</t>
+        </is>
+      </c>
+      <c r="B38" s="103" t="inlineStr">
+        <is>
+          <t>「モノづくりと同じくらいヒトづくり」を本気で重視する社風</t>
+        </is>
+      </c>
+      <c r="C38" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー／社外公開情報とも一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1" s="70"/>
+    <row r="40" ht="22" customHeight="1" s="70">
+      <c r="A40" s="105" t="inlineStr">
+        <is>
+          <t>F. 製品開発課の理念（採用基準として明文化すべき共感ポイント）</t>
+        </is>
+      </c>
+      <c r="B40" s="106" t="n"/>
+      <c r="C40" s="107" t="n"/>
+    </row>
+    <row r="41" ht="55" customHeight="1" s="70">
+      <c r="A41" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B41" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C41" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="102" t="inlineStr">
+        <is>
           <t>ミッション</t>
         </is>
       </c>
-      <c r="B38" s="103" t="inlineStr">
+      <c r="B42" s="103" t="inlineStr">
         <is>
           <t>大和合金グループが永続的に世の中に貢献し続けるための仕組み（＝技術）の創出</t>
         </is>
       </c>
-      <c r="C38" s="103" t="inlineStr">
+      <c r="C42" s="103" t="inlineStr">
         <is>
           <t>社内資料「ミッション・ビジョン・バリュー」</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1" s="70">
-      <c r="A39" s="102" t="inlineStr">
+    <row r="43" ht="60" customHeight="1" s="70">
+      <c r="A43" s="102" t="inlineStr">
         <is>
           <t>ビジョン</t>
         </is>
       </c>
-      <c r="B39" s="103" t="inlineStr">
-        <is>
-          <t>世界一の銅合金の専門家チーム。（実績例：半導体用バッキングプレート販売シェア世界一30%、ITER向け銅合金供給量世界一、航空機用メタルブッシュ世界トップレベル20%）</t>
-        </is>
-      </c>
-      <c r="C39" s="103" t="inlineStr">
+      <c r="B43" s="103" t="inlineStr">
+        <is>
+          <t>世界一の銅合金の専門家チーム。（実績例：半導体用バッキングプレート販売シェア世界一30%、ITER向け銅合金供給量世界一、航空機・自動車エンジン部品向け高強度銅合金の採用実績多数）</t>
+        </is>
+      </c>
+      <c r="C43" s="103" t="inlineStr">
         <is>
           <t>社内資料「ミッション・ビジョン・バリュー」</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="55" customHeight="1" s="70">
-      <c r="A40" s="102" t="inlineStr">
+    <row r="44" ht="20" customHeight="1" s="70">
+      <c r="A44" s="102" t="inlineStr">
         <is>
           <t>バリュー（3つ）</t>
         </is>
       </c>
-      <c r="B40" s="103" t="inlineStr">
+      <c r="B44" s="103" t="inlineStr">
         <is>
           <t>①再現性の追求（技術的エビデンスの重視）　②記録の徹底（獲得した知見の知財化・資産化）　③完遂へのこだわり（選択と集中）</t>
         </is>
       </c>
-      <c r="C40" s="103" t="inlineStr">
+      <c r="C44" s="103" t="inlineStr">
         <is>
           <t>社内資料「ミッション・ビジョン・バリュー」</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="55" customHeight="1" s="70">
-      <c r="A41" s="102" t="inlineStr">
-        <is>
-          <t>採用面接での確認ポイント（提案）</t>
-        </is>
-      </c>
-      <c r="B41" s="103" t="inlineStr">
-        <is>
-          <t>上記ミッション・ビジョン・バリューへの共感度を、面接評価票の必須項目として設計することを推奨。特に「記録の徹底」「完遂へのこだわり」は行動特性として面接で見極め可能</t>
-        </is>
-      </c>
-      <c r="C41" s="103" t="inlineStr">
-        <is>
-          <t>コンサルタント提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1" s="70">
-      <c r="A43" s="105" t="inlineStr">
-        <is>
-          <t>G. 何を成果とみなすか（評価基準・OJT設計への活用）</t>
-        </is>
-      </c>
-      <c r="B43" s="106" t="n"/>
-      <c r="C43" s="107" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1" s="70">
-      <c r="A44" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B44" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C44" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="45" ht="55" customHeight="1" s="70">
       <c r="A45" s="102" t="inlineStr">
         <is>
+          <t>採用面接での確認ポイント（提案）</t>
+        </is>
+      </c>
+      <c r="B45" s="103" t="inlineStr">
+        <is>
+          <t>上記ミッション・ビジョン・バリューへの共感度を、面接評価票の必須項目として設計することを推奨。特に「記録の徹底」「完遂へのこだわり」は行動特性として面接で見極め可能</t>
+        </is>
+      </c>
+      <c r="C45" s="103" t="inlineStr">
+        <is>
+          <t>コンサルタント提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="55" customHeight="1" s="70"/>
+    <row r="47" ht="22" customHeight="1" s="70">
+      <c r="A47" s="105" t="inlineStr">
+        <is>
+          <t>G. 何を成果とみなすか（評価基準・OJT設計への活用）</t>
+        </is>
+      </c>
+      <c r="B47" s="106" t="n"/>
+      <c r="C47" s="107" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B48" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C48" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" s="70">
+      <c r="A49" s="102" t="inlineStr">
+        <is>
           <t>短期成果（2～3ヶ月）</t>
         </is>
       </c>
-      <c r="B45" s="103" t="inlineStr">
+      <c r="B49" s="103" t="inlineStr">
         <is>
           <t>新製品・新製法開発では「仮説検証の完了数」（失敗して条件を否定できたことも成果）。既存製法改善では「標準書・手順書の改定完了件数」</t>
         </is>
       </c>
-      <c r="C45" s="103" t="inlineStr">
+      <c r="C49" s="103" t="inlineStr">
         <is>
           <t>社内資料「何を成果とみなすか」</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="55" customHeight="1" s="70">
-      <c r="A46" s="102" t="inlineStr">
-        <is>
-          <t>中期成果（半年～1年）</t>
-        </is>
-      </c>
-      <c r="B46" s="103" t="inlineStr">
-        <is>
-          <t>新製品はお客様のスペック承認・QC工程表確定の件数。新製法はパイロットテスト成功・投資判断データ完成の数。知財管理は特許出願・ノウハウ登録件数</t>
-        </is>
-      </c>
-      <c r="C46" s="103" t="inlineStr">
-        <is>
-          <t>社内資料「何を成果とみなすか」</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="55" customHeight="1" s="70">
-      <c r="A47" s="102" t="inlineStr">
-        <is>
-          <t>育成初期の目標設計への示唆</t>
-        </is>
-      </c>
-      <c r="B47" s="103" t="inlineStr">
-        <is>
-          <t>入社後は「仮説検証を完了させる」経験を積ませ、記録・報告の型を早期に習慣化させることが、江口氏の言う「地道な努力」「記録の徹底」の実践につながる</t>
-        </is>
-      </c>
-      <c r="C47" s="103" t="inlineStr">
-        <is>
-          <t>コンサルタント提案（本人インタビューと社内資料の統合）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="105" t="inlineStr">
-        <is>
-          <t>H. 社会人博士支援に関する示唆（将来の制度設計への提言）</t>
-        </is>
-      </c>
-      <c r="B48" s="106" t="n"/>
-      <c r="C48" s="107" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1" s="70">
-      <c r="A49" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B49" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C49" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="50" ht="55" customHeight="1" s="70">
       <c r="A50" s="102" t="inlineStr">
         <is>
-          <t>研究テーマと実務の関係</t>
+          <t>中期成果（半年～1年）</t>
         </is>
       </c>
       <c r="B50" s="103" t="inlineStr">
         <is>
-          <t>NC50合金開発と博士研究テーマ（結晶粒成長抑制）に直接の因果関係はないが、同じ銅合金分野での問題意識は共通していた</t>
+          <t>新製品はお客様のスペック承認・QC工程表確定の件数。新製法はパイロットテスト成功・投資判断データ完成の数。知財管理は特許出願・ノウハウ登録件数</t>
         </is>
       </c>
       <c r="C50" s="103" t="inlineStr">
         <is>
-          <t>本人インタビュー</t>
+          <t>社内資料「何を成果とみなすか」</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" s="70">
       <c r="A51" s="102" t="inlineStr">
         <is>
+          <t>育成初期の目標設計への示唆</t>
+        </is>
+      </c>
+      <c r="B51" s="103" t="inlineStr">
+        <is>
+          <t>入社後は「仮説検証を完了させる」経験を積ませ、記録・報告の型を早期に習慣化させることが、江口氏の言う「地道な努力」「記録の徹底」の実践につながる</t>
+        </is>
+      </c>
+      <c r="C51" s="103" t="inlineStr">
+        <is>
+          <t>コンサルタント提案（本人インタビューと社内資料の統合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1" s="70">
+      <c r="A52" s="105" t="inlineStr">
+        <is>
+          <t>H. 社会人博士支援に関する示唆（将来の制度設計への提言）</t>
+        </is>
+      </c>
+      <c r="B52" s="106" t="n"/>
+      <c r="C52" s="107" t="n"/>
+    </row>
+    <row r="53" ht="45" customHeight="1" s="70">
+      <c r="A53" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B53" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C53" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="55" customHeight="1" s="70">
+      <c r="A54" s="102" t="inlineStr">
+        <is>
+          <t>研究テーマと実務の関係</t>
+        </is>
+      </c>
+      <c r="B54" s="103" t="inlineStr">
+        <is>
+          <t>NC50合金開発と博士研究テーマ（結晶粒成長抑制）に直接の因果関係はないが、同じ銅合金分野での問題意識は共通していた</t>
+        </is>
+      </c>
+      <c r="C54" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" s="70">
+      <c r="A55" s="102" t="inlineStr">
+        <is>
           <t>後継者へのアドバイス</t>
         </is>
       </c>
-      <c r="B51" s="103" t="inlineStr">
+      <c r="B55" s="103" t="inlineStr">
         <is>
           <t>仕事と研究を分けて考えず、日々の業務課題をそのまま研究テーマにするべき</t>
         </is>
       </c>
-      <c r="C51" s="103" t="inlineStr">
+      <c r="C55" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="55" customHeight="1" s="70">
-      <c r="A52" s="102" t="inlineStr">
-        <is>
-          <t>会社が最優先で支援すべきこと</t>
-        </is>
-      </c>
-      <c r="B52" s="103" t="inlineStr">
-        <is>
-          <t>業務課題を研究テーマに昇華できるような、指導教員・大学との接点づくり（金銭支援や業務調整以上に重要）</t>
-        </is>
-      </c>
-      <c r="C52" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1" s="70"/>
-    <row r="54" ht="22" customHeight="1" s="70">
-      <c r="A54" s="105" t="inlineStr">
-        <is>
-          <t>I. 学術研究業績（確定情報）</t>
-        </is>
-      </c>
-      <c r="B54" s="106" t="n"/>
-      <c r="C54" s="107" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1" s="70">
-      <c r="A55" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B55" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C55" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="56" ht="75" customHeight="1" s="70">
       <c r="A56" s="102" t="inlineStr">
         <is>
+          <t>会社が最優先で支援すべきこと</t>
+        </is>
+      </c>
+      <c r="B56" s="103" t="inlineStr">
+        <is>
+          <t>業務課題を研究テーマに昇華できるような、指導教員・大学との接点づくり（金銭支援や業務調整以上に重要）</t>
+        </is>
+      </c>
+      <c r="C56" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1" s="70"/>
+    <row r="58" ht="22" customHeight="1" s="70">
+      <c r="A58" s="105" t="inlineStr">
+        <is>
+          <t>I. 学術研究業績（確定情報）</t>
+        </is>
+      </c>
+      <c r="B58" s="106" t="n"/>
+      <c r="C58" s="107" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B59" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C59" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="75" customHeight="1" s="70">
+      <c r="A60" s="102" t="inlineStr">
+        <is>
           <t>査読付き学術論文（筆頭著者・全2報）</t>
         </is>
       </c>
-      <c r="B56" s="103" t="inlineStr">
+      <c r="B60" s="103" t="inlineStr">
         <is>
           <t>①「Cu-Cr-Zr-Ag合金の機械的性質に及ぼす焼きなまし条件の影響」銅と銅合金 第51巻1号（2011）
 ②「Cu-Cr-Zr-Ag合金の焼なまし後の機械的性質及び粒成長に及ぼすAg含有量の影響」銅と銅合金 第52巻1号（2012）
 （共著：新井真人、藤井慎太朗、高山善匡 他、製品開発課の同僚と連名）</t>
         </is>
       </c>
-      <c r="C56" s="103" t="inlineStr">
+      <c r="C60" s="103" t="inlineStr">
         <is>
           <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1" s="70">
-      <c r="A57" s="102" t="inlineStr">
+    <row r="61" ht="20" customHeight="1" s="70">
+      <c r="A61" s="102" t="inlineStr">
         <is>
           <t>国際会議論文（筆頭著者）</t>
         </is>
       </c>
-      <c r="B57" s="103" t="inlineStr">
+      <c r="B61" s="103" t="inlineStr">
         <is>
           <t>"EFFECT OF Ag CONTENT ON GRAIN GROWTH DURING REVERSION IN PRECIPITATION HARDENED Cu-Cr-Zr-Ag ALLOYS" The 8th Pacific Rim International Congress on Advanced Material and Processing (PRICM8), TMS, 2013</t>
         </is>
       </c>
-      <c r="C57" s="103" t="inlineStr">
+      <c r="C61" s="103" t="inlineStr">
         <is>
           <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1" s="70">
-      <c r="A58" s="102" t="inlineStr">
-        <is>
-          <t>口頭発表</t>
-        </is>
-      </c>
-      <c r="B58" s="103" t="inlineStr">
-        <is>
-          <t>日本鋼学会 第51回・第52回講演大会（2011・2012年、いずれも筆頭発表者）、PRICM8国際会議（2013年、筆頭発表者）</t>
-        </is>
-      </c>
-      <c r="C58" s="103" t="inlineStr">
-        <is>
-          <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1" s="70">
-      <c r="A60" s="105" t="inlineStr">
-        <is>
-          <t>J. 企業文化としての「博士人材」の裏付け</t>
-        </is>
-      </c>
-      <c r="B60" s="106" t="n"/>
-      <c r="C60" s="107" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1" s="70">
-      <c r="A61" s="101" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B61" s="101" t="inlineStr">
-        <is>
-          <t>要件・内容</t>
-        </is>
-      </c>
-      <c r="C61" s="101" t="inlineStr">
-        <is>
-          <t>根拠</t>
         </is>
       </c>
     </row>
     <row r="62" ht="65" customHeight="1" s="70">
       <c r="A62" s="102" t="inlineStr">
         <is>
+          <t>口頭発表</t>
+        </is>
+      </c>
+      <c r="B62" s="103" t="inlineStr">
+        <is>
+          <t>日本鋼学会 第51回・第52回講演大会（2011・2012年、いずれも筆頭発表者）、PRICM8国際会議（2013年、筆頭発表者）</t>
+        </is>
+      </c>
+      <c r="C62" s="103" t="inlineStr">
+        <is>
+          <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="55" customHeight="1" s="70"/>
+    <row r="64" ht="22" customHeight="1" s="70">
+      <c r="A64" s="105" t="inlineStr">
+        <is>
+          <t>J. 企業文化としての「博士人材」の裏付け</t>
+        </is>
+      </c>
+      <c r="B64" s="106" t="n"/>
+      <c r="C64" s="107" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B65" s="101" t="inlineStr">
+        <is>
+          <t>要件・内容</t>
+        </is>
+      </c>
+      <c r="C65" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="102" t="inlineStr">
+        <is>
           <t>経営陣も博士号取得者</t>
         </is>
       </c>
-      <c r="B62" s="103" t="inlineStr">
+      <c r="B66" s="103" t="inlineStr">
         <is>
           <t>大和合金株式会社の代表取締役・萩野源次郎社長も2010年度に博士号を取得。江口氏は謝辞にて「暖かい激励とアドバイスを頂いた」と記載。技術を経営層自らが体系化する文化が存在することを裏付け</t>
         </is>
       </c>
-      <c r="C62" s="103" t="inlineStr">
+      <c r="C66" s="103" t="inlineStr">
         <is>
           <t>学位論文謝辞</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="55" customHeight="1" s="70">
-      <c r="A63" s="102" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="102" t="inlineStr">
         <is>
           <t>社外の技術顧問体制</t>
         </is>
       </c>
-      <c r="B63" s="103" t="inlineStr">
+      <c r="B67" s="103" t="inlineStr">
         <is>
           <t>古河電気工業出身の工学博士（元研究開発部技師長）が技術顧問として長年指導。社会人ドクター取得を会社として後押しする土壌がある</t>
         </is>
       </c>
-      <c r="C63" s="103" t="inlineStr">
+      <c r="C67" s="103" t="inlineStr">
         <is>
           <t>学位論文謝辞</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="55" customHeight="1" s="70">
-      <c r="A64" s="102" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="102" t="inlineStr">
         <is>
           <t>共同研究チームの存在</t>
         </is>
       </c>
-      <c r="B64" s="103" t="inlineStr">
+      <c r="B68" s="103" t="inlineStr">
         <is>
           <t>製品開発課の同僚（新井真人係長、藤井慎太朗氏ほか）が実験全般を推進し、社会人ドクターの研究をチームでサポート。1人で抱え込まず組織的に取り組む文化</t>
         </is>
       </c>
-      <c r="C64" s="103" t="inlineStr">
+      <c r="C68" s="103" t="inlineStr">
         <is>
           <t>学位論文謝辞</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A60:C60"/>
+  <mergeCells count="13">
     <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -3221,7 +3221,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="35" customHeight="1" s="70">
+    <row r="12" ht="50" customHeight="1" s="70">
       <c r="A12" s="102" t="inlineStr">
         <is>
           <t>専門分野</t>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C12" s="103" t="inlineStr">
         <is>
-          <t>非鉄金属材料（特に銅合金）に関する知識、または金属材料全般の基礎知識</t>
+          <t>非鉄金属材料（特に銅合金）に関する知識、または金属材料全般の基礎知識。化学成分分析（原子吸光分析等）や機械的性質・導電率検査など、分析・検査の実務経験があれば理解が早い</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="35" customHeight="1" s="70">
+    <row r="30" ht="85" customHeight="1" s="70">
       <c r="A30" s="102" t="inlineStr">
         <is>
           <t>入社～3年</t>
@@ -3457,7 +3457,7 @@
       <c r="B30" s="102" t="inlineStr"/>
       <c r="C30" s="103" t="inlineStr">
         <is>
-          <t>製造・品質保証など現場配属で「モノづくりの基盤」を体得</t>
+          <t>製造・品質保証など現場配属で「モノづくりの基盤」を体得。（ロールモデル例：溶解係で原料・合金要素の性質を体得 → 品質保証（検査）で原子吸光分析・機械的性質検査・導電率検査を担当し組織と強度のバラつきに向き合う → 砂型鋳造係で凝固過程と結晶粒組織の関係を体得し、鋳型作りから出荷までの一貫工程で納期遵守の重要性を学ぶ）</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="35" customHeight="1" s="70">
+    <row r="43" ht="55" customHeight="1" s="70">
       <c r="A43" s="102" t="inlineStr">
         <is>
           <t>現場主義</t>
@@ -3592,7 +3592,7 @@
       <c r="B43" s="102" t="inlineStr"/>
       <c r="C43" s="103" t="inlineStr">
         <is>
-          <t>「データや報告だけでなく、自分の目で現場を確かめに行った経験はありますか」</t>
+          <t>「データや報告だけでなく、自分の目で現場を確かめに行った経験はありますか」／「自分の部門の都合だけでなく、前工程・後工程への影響を考えて動いた経験はありますか」</t>
         </is>
       </c>
     </row>
@@ -3644,10 +3644,10 @@
       <c r="B48" s="106" t="n"/>
       <c r="C48" s="107" t="n"/>
     </row>
-    <row r="49" ht="70" customHeight="1" s="70">
+    <row r="49" ht="85" customHeight="1" s="70">
       <c r="A49" s="103" t="inlineStr">
         <is>
-          <t>製造→品質保証→製造→製品開発課→朝霞工場長→取締役本社工場長。修士卒で入社後、在籍しながら社会人ドクターとして宇都宮大学で博士号（工学）を取得（2014年）。ITER（核融合炉）向け銅合金の国家研究機関との共同開発、本田技研工業とのF1エンジン用コンロッドメタル共同開発・特許共同出願など、現場経験を土台に外部と対等に渡り合う技術者として成長した実例。詳細は「中核人材ペルソナ（案）」シートを参照。</t>
+          <t>製造（溶解係）→品質保証（検査：原子吸光分析・機械的性質・導電率）→製造（砂型鋳造係）→製品開発課→朝霞工場長→取締役本社工場長。修士卒で入社後、在籍しながら社会人ドクターとして宇都宮大学で博士号（工学）を取得（2014年）。ITER（核融合炉）向け銅合金の国家研究機関との共同開発、本田技研工業とのF1エンジン用コンロッドメタル共同開発・特許共同出願など、現場経験を土台に外部と対等に渡り合う技術者として成長した実例。詳細は「中核人材ペルソナ（案）」シートを参照。</t>
         </is>
       </c>
       <c r="B49" s="106" t="n"/>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -2383,7 +2383,7 @@
     <row r="17" ht="22" customHeight="1" s="70">
       <c r="A17" s="105" t="inlineStr">
         <is>
-          <t>B. キャリアの転機（朝霞工場長時代の具体的実績）</t>
+          <t>B. キャリアの転機（具体的実績）</t>
         </is>
       </c>
       <c r="B17" s="106" t="n"/>
@@ -2406,58 +2406,58 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="70" customHeight="1" s="70">
       <c r="A19" s="102" t="inlineStr">
         <is>
-          <t>実績①：現場改革</t>
+          <t>実績①（製品開発課係長時代）：国家プロジェクト級の共同開発</t>
         </is>
       </c>
       <c r="B19" s="103" t="inlineStr">
         <is>
+          <t>核融合炉（ITER＝国際熱核融合実験炉）向け銅合金の開発で、国の研究機関の研究員と対等に議論しながら新製品化。同分野で大和合金グループは世界供給量No.1の実績を保有</t>
+        </is>
+      </c>
+      <c r="C19" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー＋社内ビジョン資料（製品開発課のビジョン：ITER採用実績）との一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1" s="70">
+      <c r="A20" s="102" t="inlineStr">
+        <is>
+          <t>実績②（製品開発課係長時代）：大手企業との共同開発</t>
+        </is>
+      </c>
+      <c r="B20" s="103" t="inlineStr">
+        <is>
+          <t>本田技研工業とのすべり軸受（F1エンジン用コンロッドメタル）の共同開発。ベリリウム銅代替のコルソン系銅合金「NC50合金」（高強度・高熱伝導性）を採用し、製法特許を本田技研工業と共同出願・取得。F1車に実採用された</t>
+        </is>
+      </c>
+      <c r="C20" s="103" t="inlineStr">
+        <is>
+          <t>本人インタビュー＋日刊鉄鋼新聞（Japan Metal Daily）報道「エンジン部品用銅合金／三芳合金が特許取得／本田技研と共同 F1車に採用」で外部裏付け済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="70" customHeight="1" s="70">
+      <c r="A21" s="102" t="inlineStr">
+        <is>
+          <t>実績③（朝霞工場長時代）：現場改革</t>
+        </is>
+      </c>
+      <c r="B21" s="103" t="inlineStr">
+        <is>
           <t>朝霞工場で2S活動・生産性改善を主導。現場の意識改革（毎日の2Sを習慣化する文化づくり）により、過去最高の出荷重量を「当たり前」に出せる体制を実現。最大の苦労は短期的な生産優先との時間配分バランス</t>
         </is>
       </c>
-      <c r="C19" s="103" t="inlineStr">
+      <c r="C21" s="103" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1" s="70">
-      <c r="A20" s="102" t="inlineStr">
-        <is>
-          <t>実績②：国家プロジェクト級の共同開発</t>
-        </is>
-      </c>
-      <c r="B20" s="103" t="inlineStr">
-        <is>
-          <t>核融合炉（ITER＝国際熱核融合実験炉）向け銅合金の開発で、国の研究機関の研究員と対等に議論しながら新製品化。同分野で大和合金グループは世界供給量No.1の実績を保有</t>
-        </is>
-      </c>
-      <c r="C20" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー＋社内ビジョン資料（製品開発課のビジョン：ITER採用実績）との一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" s="70">
-      <c r="A21" s="102" t="inlineStr">
-        <is>
-          <t>実績③：大手企業との共同開発</t>
-        </is>
-      </c>
-      <c r="B21" s="103" t="inlineStr">
-        <is>
-          <t>本田技研工業とのすべり軸受（F1エンジン用コンロッドメタル）の共同開発。ベリリウム銅代替のコルソン系銅合金「NC50合金」（高強度・高熱伝導性）を採用し、製法特許を本田技研工業と共同出願・取得。F1車に実採用された</t>
-        </is>
-      </c>
-      <c r="C21" s="103" t="inlineStr">
-        <is>
-          <t>本人インタビュー＋日刊鉄鋼新聞（Japan Metal Daily）報道「エンジン部品用銅合金／三芳合金が特許取得／本田技研と共同 F1車に採用」で外部裏付け済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="55" customHeight="1" s="70">
+    <row r="22" ht="70" customHeight="1" s="70">
       <c r="A22" s="102" t="inlineStr">
         <is>
           <t>ターニングポイントの本質</t>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="B22" s="103" t="inlineStr">
         <is>
-          <t>大手企業・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただしそれは、現場のモノづくりを広く経験した基盤があってこそ</t>
+          <t>製品開発課係長時代、大手企業・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただしそれは、現場のモノづくり（溶解係・砂型鋳造係・品質保証）を広く経験した基盤があってこそ</t>
         </is>
       </c>
       <c r="C22" s="103" t="inlineStr">
@@ -3644,10 +3644,10 @@
       <c r="B48" s="106" t="n"/>
       <c r="C48" s="107" t="n"/>
     </row>
-    <row r="49" ht="85" customHeight="1" s="70">
+    <row r="49" ht="95" customHeight="1" s="70">
       <c r="A49" s="103" t="inlineStr">
         <is>
-          <t>製造（溶解係）→品質保証（検査：原子吸光分析・機械的性質・導電率）→製造（砂型鋳造係）→製品開発課→朝霞工場長→取締役本社工場長。修士卒で入社後、在籍しながら社会人ドクターとして宇都宮大学で博士号（工学）を取得（2014年）。ITER（核融合炉）向け銅合金の国家研究機関との共同開発、本田技研工業とのF1エンジン用コンロッドメタル共同開発・特許共同出願など、現場経験を土台に外部と対等に渡り合う技術者として成長した実例。詳細は「中核人材ペルソナ（案）」シートを参照。</t>
+          <t>製造（溶解係）→品質保証（検査：原子吸光分析・機械的性質・導電率）→製造（砂型鋳造係）→製品開発課（係長）→朝霞工場長→取締役本社工場長。修士卒で入社後、在籍しながら社会人ドクターとして宇都宮大学で博士号（工学）を取得（2014年）。製品開発課係長時代にITER（核融合炉）向け銅合金の国家研究機関との共同開発、本田技研工業とのF1エンジン用コンロッドメタル共同開発・特許共同出願を実現し、朝霞工場長時代には2S活動・生産性改善で現場改革を主導。現場経験を土台に外部と対等に渡り合う技術者として成長した実例。詳細は「中核人材ペルソナ（案）」シートを参照。</t>
         </is>
       </c>
       <c r="B49" s="106" t="n"/>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -285,6 +285,12 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -945,7 +951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1272,6 +1278,9 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2184,7 +2193,7 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" s="70">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="111" t="inlineStr">
         <is>
           <t>※第2回コンサルティング（中核人材ペルソナ設計と採用基準の言語化）での使用を想定した素案。本人インタビューおよび「製品開発課の理念」「ミッション・ビジョン・バリュー」「何を成果とみなすか」の社内資料をもとに作成。</t>
         </is>
@@ -2217,102 +2226,102 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="70">
-      <c r="A5" s="102" t="inlineStr">
+      <c r="A5" s="112" t="inlineStr">
         <is>
           <t>キャリアパス</t>
         </is>
       </c>
-      <c r="B5" s="103" t="inlineStr">
+      <c r="B5" s="114" t="inlineStr">
         <is>
           <t>製造（溶解係） → 品質保証（検査） → 製造（砂型鋳造係） → 製品開発課 → 朝霞工場長 → 取締役 本社工場長</t>
         </is>
       </c>
-      <c r="C5" s="103" t="inlineStr">
+      <c r="C5" s="114" t="inlineStr">
         <is>
           <t>本人申告</t>
         </is>
       </c>
     </row>
     <row r="6" ht="55" customHeight="1" s="70">
-      <c r="A6" s="102" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>溶解係での経験</t>
         </is>
       </c>
-      <c r="B6" s="103" t="inlineStr">
+      <c r="B6" s="114" t="inlineStr">
         <is>
           <t>原料・合金要素の性質への感覚的理解が最も活き、次いで溶解温度・成分調整の勘、異常の兆候を先取りする感覚の原点もここで培われた（本人の優先順位付けによる）</t>
         </is>
       </c>
-      <c r="C6" s="103" t="inlineStr">
+      <c r="C6" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="7" ht="65" customHeight="1" s="70">
-      <c r="A7" s="102" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>品質保証（検査）での経験</t>
         </is>
       </c>
-      <c r="B7" s="103" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
         <is>
           <t>主に検査を担当。原子吸光分析によるインゴットの化学成分分析、機械的性質（引張・硬さ）検査、導電率検査を実施。特に機械的性質検査で組織と強度のバラつきに日々直面したことが、博士研究（結晶粒成長抑制・機械的性質）への問題意識に直結</t>
         </is>
       </c>
-      <c r="C7" s="103" t="inlineStr">
+      <c r="C7" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="8" ht="65" customHeight="1" s="70">
-      <c r="A8" s="102" t="inlineStr">
+      <c r="A8" s="112" t="inlineStr">
         <is>
           <t>砂型鋳造係での経験</t>
         </is>
       </c>
-      <c r="B8" s="103" t="inlineStr">
+      <c r="B8" s="114" t="inlineStr">
         <is>
           <t>冷却速度・凝固過程と組織（結晶粒）の関係を感覚的に理解（博士研究テーマの現場的原体験）。鋳型作りから溶解・鋳造、仕上、出荷までが一貫して完結する工程であり、納期を守ることの大切さを学んだ</t>
         </is>
       </c>
-      <c r="C8" s="103" t="inlineStr">
+      <c r="C8" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="9" ht="65" customHeight="1" s="70">
-      <c r="A9" s="102" t="inlineStr">
+      <c r="A9" s="112" t="inlineStr">
         <is>
           <t>部門横断経験の意味</t>
         </is>
       </c>
-      <c r="B9" s="103" t="inlineStr">
+      <c r="B9" s="114" t="inlineStr">
         <is>
           <t>溶解係→品質保証→砂型鋳造係と複数部門を経験したことで、各部門が見ている指標・価値基準の違いを実感できたことに最も意味があった。後継者が理解できているかは、「自部門の都合だけでなく、前工程・後工程への影響を自然に口にするか」で見極められる</t>
         </is>
       </c>
-      <c r="C9" s="103" t="inlineStr">
+      <c r="C9" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="10" ht="85" customHeight="1" s="70">
-      <c r="A10" s="102" t="inlineStr">
+      <c r="A10" s="112" t="inlineStr">
         <is>
           <t>入社時の学歴</t>
         </is>
       </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="B10" s="114" t="inlineStr">
         <is>
           <t>修士卒で入社。その後、在籍しながら社会人学生として博士号（宇都宮大学）を取得</t>
         </is>
       </c>
-      <c r="C10" s="103" t="inlineStr">
+      <c r="C10" s="114" t="inlineStr">
         <is>
           <t>本人申告</t>
         </is>
@@ -2346,34 +2355,34 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" s="70">
-      <c r="A14" s="102" t="inlineStr">
+      <c r="A14" s="112" t="inlineStr">
         <is>
           <t>博士論文テーマ</t>
         </is>
       </c>
-      <c r="B14" s="103" t="inlineStr">
+      <c r="B14" s="114" t="inlineStr">
         <is>
           <t>「析出強化型Cu-Cr-Zr系合金の耐熱性改善に関する研究」（2014年、宇都宮大学大学院工学研究科システム創成工学専攻、指導教員：高山善匡教授）。三芳合金工業在職中の2011～2013年度、社会人ドクターとして取得。Cu-Cr-Zr系銅合金にAgを0～1.2mass%添加し、900℃復元中の結晶粒成長挙動・耐熱性への影響を解明。Ag添加により析出強化量・固溶強化量が向上し、Ag濃度0.57mass%で耐熱強度23%改善、1.13mass%で約40%改善を実証</t>
         </is>
       </c>
-      <c r="C14" s="103" t="inlineStr">
+      <c r="C14" s="114" t="inlineStr">
         <is>
           <t>学位論文本文（原本確認済み）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="65" customHeight="1" s="70">
-      <c r="A15" s="102" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>進学の経緯／在学形態</t>
         </is>
       </c>
-      <c r="B15" s="103" t="inlineStr">
+      <c r="B15" s="114" t="inlineStr">
         <is>
           <t>社長の人脈による縁、かつ宇都宮大学で非鉄金属の研究が行われていたことが理由。会社に在籍しながら社会人学生として取得（休職・離職なし）</t>
         </is>
       </c>
-      <c r="C15" s="103" t="inlineStr">
+      <c r="C15" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
@@ -2407,68 +2416,68 @@
       </c>
     </row>
     <row r="19" ht="70" customHeight="1" s="70">
-      <c r="A19" s="102" t="inlineStr">
+      <c r="A19" s="112" t="inlineStr">
         <is>
           <t>実績①（製品開発課係長時代）：国家プロジェクト級の共同開発</t>
         </is>
       </c>
-      <c r="B19" s="103" t="inlineStr">
+      <c r="B19" s="114" t="inlineStr">
         <is>
           <t>核融合炉（ITER＝国際熱核融合実験炉）向け銅合金の開発で、国の研究機関の研究員と対等に議論しながら新製品化。同分野で大和合金グループは世界供給量No.1の実績を保有</t>
         </is>
       </c>
-      <c r="C19" s="103" t="inlineStr">
+      <c r="C19" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー＋社内ビジョン資料（製品開発課のビジョン：ITER採用実績）との一致</t>
         </is>
       </c>
     </row>
     <row r="20" ht="70" customHeight="1" s="70">
-      <c r="A20" s="102" t="inlineStr">
+      <c r="A20" s="112" t="inlineStr">
         <is>
           <t>実績②（製品開発課係長時代）：大手企業との共同開発</t>
         </is>
       </c>
-      <c r="B20" s="103" t="inlineStr">
+      <c r="B20" s="114" t="inlineStr">
         <is>
           <t>本田技研工業とのすべり軸受（F1エンジン用コンロッドメタル）の共同開発。ベリリウム銅代替のコルソン系銅合金「NC50合金」（高強度・高熱伝導性）を採用し、製法特許を本田技研工業と共同出願・取得。F1車に実採用された</t>
         </is>
       </c>
-      <c r="C20" s="103" t="inlineStr">
+      <c r="C20" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー＋日刊鉄鋼新聞（Japan Metal Daily）報道「エンジン部品用銅合金／三芳合金が特許取得／本田技研と共同 F1車に採用」で外部裏付け済み</t>
         </is>
       </c>
     </row>
     <row r="21" ht="70" customHeight="1" s="70">
-      <c r="A21" s="102" t="inlineStr">
+      <c r="A21" s="112" t="inlineStr">
         <is>
           <t>実績③（朝霞工場長時代）：現場改革</t>
         </is>
       </c>
-      <c r="B21" s="103" t="inlineStr">
+      <c r="B21" s="114" t="inlineStr">
         <is>
           <t>朝霞工場で2S活動・生産性改善を主導。現場の意識改革（毎日の2Sを習慣化する文化づくり）により、過去最高の出荷重量を「当たり前」に出せる体制を実現。最大の苦労は短期的な生産優先との時間配分バランス</t>
         </is>
       </c>
-      <c r="C21" s="103" t="inlineStr">
+      <c r="C21" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="22" ht="70" customHeight="1" s="70">
-      <c r="A22" s="102" t="inlineStr">
+      <c r="A22" s="112" t="inlineStr">
         <is>
           <t>ターニングポイントの本質</t>
         </is>
       </c>
-      <c r="B22" s="103" t="inlineStr">
+      <c r="B22" s="114" t="inlineStr">
         <is>
           <t>製品開発課係長時代、大手企業・国の研究機関の研究員と対等に議論を戦わせながら新製品を開発した経験。ただしそれは、現場のモノづくり（溶解係・砂型鋳造係・品質保証）を広く経験した基盤があってこそ</t>
         </is>
       </c>
-      <c r="C22" s="103" t="inlineStr">
+      <c r="C22" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
@@ -2502,35 +2511,35 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" s="70">
-      <c r="A26" s="102" t="inlineStr">
+      <c r="A26" s="112" t="inlineStr">
         <is>
           <t>現在の強み</t>
         </is>
       </c>
-      <c r="B26" s="103" t="inlineStr">
+      <c r="B26" s="114" t="inlineStr">
         <is>
           <t>① 製造・品質・開発の全部門を俯瞰した技術判断力
 ② 外部（大手企業・国の研究機関）と対等に議論できる専門性・発信力</t>
         </is>
       </c>
-      <c r="C26" s="103" t="inlineStr">
+      <c r="C26" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="27" ht="55" customHeight="1" s="70">
-      <c r="A27" s="102" t="inlineStr">
+      <c r="A27" s="112" t="inlineStr">
         <is>
           <t>暗黙知・勘所</t>
         </is>
       </c>
-      <c r="B27" s="103" t="inlineStr">
+      <c r="B27" s="114" t="inlineStr">
         <is>
           <t>不良・異常の兆候を先取りして見抜く力（10～20年かけて培われる現場感覚）</t>
         </is>
       </c>
-      <c r="C27" s="103" t="inlineStr">
+      <c r="C27" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
@@ -2564,73 +2573,74 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="102" t="inlineStr">
+      <c r="A31" s="112" t="inlineStr">
         <is>
           <t>必須の資質（優先順位順）</t>
         </is>
       </c>
-      <c r="B31" s="103" t="inlineStr">
+      <c r="B31" s="114" t="inlineStr">
         <is>
           <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢（現場主義）　＞　③立場の違う人と対等に議論できる度胸</t>
         </is>
       </c>
-      <c r="C31" s="103" t="inlineStr">
+      <c r="C31" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1" s="70">
-      <c r="A32" s="102" t="inlineStr">
+      <c r="A32" s="112" t="inlineStr">
         <is>
           <t>「任せられる」と判断する決め手</t>
         </is>
       </c>
-      <c r="B32" s="103" t="inlineStr">
+      <c r="B32" s="114" t="inlineStr">
         <is>
           <t>失敗への向き合い方（逃げずに原因を追究できるか）</t>
         </is>
       </c>
-      <c r="C32" s="103" t="inlineStr">
+      <c r="C32" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" s="70">
-      <c r="A33" s="102" t="inlineStr">
+      <c r="A33" s="112" t="inlineStr">
         <is>
           <t>NG条件</t>
         </is>
       </c>
-      <c r="B33" s="103" t="inlineStr">
+      <c r="B33" s="114" t="inlineStr">
         <is>
           <t>都合の悪い情報を隠す・報告を遅らせる姿勢</t>
         </is>
       </c>
-      <c r="C33" s="103" t="inlineStr">
+      <c r="C33" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1" s="70">
-      <c r="A34" s="102" t="inlineStr">
+      <c r="A34" s="112" t="inlineStr">
         <is>
           <t>有効だった育成環境</t>
         </is>
       </c>
-      <c r="B34" s="103" t="inlineStr">
+      <c r="B34" s="114" t="inlineStr">
         <is>
           <t>外部の研究者・他社との共同開発の機会を与えられたこと</t>
         </is>
       </c>
-      <c r="C34" s="103" t="inlineStr">
+      <c r="C34" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="22" customHeight="1" s="70">
       <c r="A36" s="105" t="inlineStr">
         <is>
@@ -2658,17 +2668,17 @@
       </c>
     </row>
     <row r="38" ht="40" customHeight="1" s="70">
-      <c r="A38" s="102" t="inlineStr">
+      <c r="A38" s="112" t="inlineStr">
         <is>
           <t>大和合金ならではの文化</t>
         </is>
       </c>
-      <c r="B38" s="103" t="inlineStr">
+      <c r="B38" s="114" t="inlineStr">
         <is>
           <t>「モノづくりと同じくらいヒトづくり」を本気で重視する社風</t>
         </is>
       </c>
-      <c r="C38" s="103" t="inlineStr">
+      <c r="C38" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー／社外公開情報とも一致</t>
         </is>
@@ -2702,68 +2712,68 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="102" t="inlineStr">
+      <c r="A42" s="112" t="inlineStr">
         <is>
           <t>ミッション</t>
         </is>
       </c>
-      <c r="B42" s="103" t="inlineStr">
+      <c r="B42" s="114" t="inlineStr">
         <is>
           <t>大和合金グループが永続的に世の中に貢献し続けるための仕組み（＝技術）の創出</t>
         </is>
       </c>
-      <c r="C42" s="103" t="inlineStr">
+      <c r="C42" s="114" t="inlineStr">
         <is>
           <t>社内資料「ミッション・ビジョン・バリュー」</t>
         </is>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1" s="70">
-      <c r="A43" s="102" t="inlineStr">
+      <c r="A43" s="112" t="inlineStr">
         <is>
           <t>ビジョン</t>
         </is>
       </c>
-      <c r="B43" s="103" t="inlineStr">
+      <c r="B43" s="114" t="inlineStr">
         <is>
           <t>世界一の銅合金の専門家チーム。（実績例：半導体用バッキングプレート販売シェア世界一30%、ITER向け銅合金供給量世界一、航空機・自動車エンジン部品向け高強度銅合金の採用実績多数）</t>
         </is>
       </c>
-      <c r="C43" s="103" t="inlineStr">
+      <c r="C43" s="114" t="inlineStr">
         <is>
           <t>社内資料「ミッション・ビジョン・バリュー」</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" s="70">
-      <c r="A44" s="102" t="inlineStr">
+      <c r="A44" s="112" t="inlineStr">
         <is>
           <t>バリュー（3つ）</t>
         </is>
       </c>
-      <c r="B44" s="103" t="inlineStr">
+      <c r="B44" s="114" t="inlineStr">
         <is>
           <t>①再現性の追求（技術的エビデンスの重視）　②記録の徹底（獲得した知見の知財化・資産化）　③完遂へのこだわり（選択と集中）</t>
         </is>
       </c>
-      <c r="C44" s="103" t="inlineStr">
+      <c r="C44" s="114" t="inlineStr">
         <is>
           <t>社内資料「ミッション・ビジョン・バリュー」</t>
         </is>
       </c>
     </row>
     <row r="45" ht="55" customHeight="1" s="70">
-      <c r="A45" s="102" t="inlineStr">
+      <c r="A45" s="112" t="inlineStr">
         <is>
           <t>採用面接での確認ポイント（提案）</t>
         </is>
       </c>
-      <c r="B45" s="103" t="inlineStr">
+      <c r="B45" s="114" t="inlineStr">
         <is>
           <t>上記ミッション・ビジョン・バリューへの共感度を、面接評価票の必須項目として設計することを推奨。特に「記録の徹底」「完遂へのこだわり」は行動特性として面接で見極め可能</t>
         </is>
       </c>
-      <c r="C45" s="103" t="inlineStr">
+      <c r="C45" s="114" t="inlineStr">
         <is>
           <t>コンサルタント提案</t>
         </is>
@@ -2797,51 +2807,51 @@
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" s="70">
-      <c r="A49" s="102" t="inlineStr">
+      <c r="A49" s="112" t="inlineStr">
         <is>
           <t>短期成果（2～3ヶ月）</t>
         </is>
       </c>
-      <c r="B49" s="103" t="inlineStr">
+      <c r="B49" s="114" t="inlineStr">
         <is>
           <t>新製品・新製法開発では「仮説検証の完了数」（失敗して条件を否定できたことも成果）。既存製法改善では「標準書・手順書の改定完了件数」</t>
         </is>
       </c>
-      <c r="C49" s="103" t="inlineStr">
+      <c r="C49" s="114" t="inlineStr">
         <is>
           <t>社内資料「何を成果とみなすか」</t>
         </is>
       </c>
     </row>
     <row r="50" ht="55" customHeight="1" s="70">
-      <c r="A50" s="102" t="inlineStr">
+      <c r="A50" s="112" t="inlineStr">
         <is>
           <t>中期成果（半年～1年）</t>
         </is>
       </c>
-      <c r="B50" s="103" t="inlineStr">
+      <c r="B50" s="114" t="inlineStr">
         <is>
           <t>新製品はお客様のスペック承認・QC工程表確定の件数。新製法はパイロットテスト成功・投資判断データ完成の数。知財管理は特許出願・ノウハウ登録件数</t>
         </is>
       </c>
-      <c r="C50" s="103" t="inlineStr">
+      <c r="C50" s="114" t="inlineStr">
         <is>
           <t>社内資料「何を成果とみなすか」</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" s="70">
-      <c r="A51" s="102" t="inlineStr">
+      <c r="A51" s="112" t="inlineStr">
         <is>
           <t>育成初期の目標設計への示唆</t>
         </is>
       </c>
-      <c r="B51" s="103" t="inlineStr">
+      <c r="B51" s="114" t="inlineStr">
         <is>
           <t>入社後は「仮説検証を完了させる」経験を積ませ、記録・報告の型を早期に習慣化させることが、江口氏の言う「地道な努力」「記録の徹底」の実践につながる</t>
         </is>
       </c>
-      <c r="C51" s="103" t="inlineStr">
+      <c r="C51" s="114" t="inlineStr">
         <is>
           <t>コンサルタント提案（本人インタビューと社内資料の統合）</t>
         </is>
@@ -2874,51 +2884,51 @@
       </c>
     </row>
     <row r="54" ht="55" customHeight="1" s="70">
-      <c r="A54" s="102" t="inlineStr">
+      <c r="A54" s="112" t="inlineStr">
         <is>
           <t>研究テーマと実務の関係</t>
         </is>
       </c>
-      <c r="B54" s="103" t="inlineStr">
+      <c r="B54" s="114" t="inlineStr">
         <is>
           <t>NC50合金開発と博士研究テーマ（結晶粒成長抑制）に直接の因果関係はないが、同じ銅合金分野での問題意識は共通していた</t>
         </is>
       </c>
-      <c r="C54" s="103" t="inlineStr">
+      <c r="C54" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" s="70">
-      <c r="A55" s="102" t="inlineStr">
+      <c r="A55" s="112" t="inlineStr">
         <is>
           <t>後継者へのアドバイス</t>
         </is>
       </c>
-      <c r="B55" s="103" t="inlineStr">
+      <c r="B55" s="114" t="inlineStr">
         <is>
           <t>仕事と研究を分けて考えず、日々の業務課題をそのまま研究テーマにするべき</t>
         </is>
       </c>
-      <c r="C55" s="103" t="inlineStr">
+      <c r="C55" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
       </c>
     </row>
     <row r="56" ht="75" customHeight="1" s="70">
-      <c r="A56" s="102" t="inlineStr">
+      <c r="A56" s="112" t="inlineStr">
         <is>
           <t>会社が最優先で支援すべきこと</t>
         </is>
       </c>
-      <c r="B56" s="103" t="inlineStr">
+      <c r="B56" s="114" t="inlineStr">
         <is>
           <t>業務課題を研究テーマに昇華できるような、指導教員・大学との接点づくり（金銭支援や業務調整以上に重要）</t>
         </is>
       </c>
-      <c r="C56" s="103" t="inlineStr">
+      <c r="C56" s="114" t="inlineStr">
         <is>
           <t>本人インタビュー</t>
         </is>
@@ -2952,53 +2962,53 @@
       </c>
     </row>
     <row r="60" ht="75" customHeight="1" s="70">
-      <c r="A60" s="102" t="inlineStr">
+      <c r="A60" s="112" t="inlineStr">
         <is>
           <t>査読付き学術論文（筆頭著者・全2報）</t>
         </is>
       </c>
-      <c r="B60" s="103" t="inlineStr">
+      <c r="B60" s="114" t="inlineStr">
         <is>
           <t>①「Cu-Cr-Zr-Ag合金の機械的性質に及ぼす焼きなまし条件の影響」銅と銅合金 第51巻1号（2011）
 ②「Cu-Cr-Zr-Ag合金の焼なまし後の機械的性質及び粒成長に及ぼすAg含有量の影響」銅と銅合金 第52巻1号（2012）
 （共著：新井真人、藤井慎太朗、高山善匡 他、製品開発課の同僚と連名）</t>
         </is>
       </c>
-      <c r="C60" s="103" t="inlineStr">
+      <c r="C60" s="114" t="inlineStr">
         <is>
           <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" s="70">
-      <c r="A61" s="102" t="inlineStr">
+      <c r="A61" s="112" t="inlineStr">
         <is>
           <t>国際会議論文（筆頭著者）</t>
         </is>
       </c>
-      <c r="B61" s="103" t="inlineStr">
+      <c r="B61" s="114" t="inlineStr">
         <is>
           <t>"EFFECT OF Ag CONTENT ON GRAIN GROWTH DURING REVERSION IN PRECIPITATION HARDENED Cu-Cr-Zr-Ag ALLOYS" The 8th Pacific Rim International Congress on Advanced Material and Processing (PRICM8), TMS, 2013</t>
         </is>
       </c>
-      <c r="C61" s="103" t="inlineStr">
+      <c r="C61" s="114" t="inlineStr">
         <is>
           <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
         </is>
       </c>
     </row>
     <row r="62" ht="65" customHeight="1" s="70">
-      <c r="A62" s="102" t="inlineStr">
+      <c r="A62" s="112" t="inlineStr">
         <is>
           <t>口頭発表</t>
         </is>
       </c>
-      <c r="B62" s="103" t="inlineStr">
+      <c r="B62" s="114" t="inlineStr">
         <is>
           <t>日本鋼学会 第51回・第52回講演大会（2011・2012年、いずれも筆頭発表者）、PRICM8国際会議（2013年、筆頭発表者）</t>
         </is>
       </c>
-      <c r="C62" s="103" t="inlineStr">
+      <c r="C62" s="114" t="inlineStr">
         <is>
           <t>学位論文「本研究に関する掲載論文と口頭発表論文」</t>
         </is>
@@ -3032,51 +3042,51 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="102" t="inlineStr">
+      <c r="A66" s="112" t="inlineStr">
         <is>
           <t>経営陣も博士号取得者</t>
         </is>
       </c>
-      <c r="B66" s="103" t="inlineStr">
+      <c r="B66" s="114" t="inlineStr">
         <is>
           <t>大和合金株式会社の代表取締役・萩野源次郎社長も2010年度に博士号を取得。江口氏は謝辞にて「暖かい激励とアドバイスを頂いた」と記載。技術を経営層自らが体系化する文化が存在することを裏付け</t>
         </is>
       </c>
-      <c r="C66" s="103" t="inlineStr">
+      <c r="C66" s="114" t="inlineStr">
         <is>
           <t>学位論文謝辞</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="102" t="inlineStr">
+      <c r="A67" s="112" t="inlineStr">
         <is>
           <t>社外の技術顧問体制</t>
         </is>
       </c>
-      <c r="B67" s="103" t="inlineStr">
+      <c r="B67" s="114" t="inlineStr">
         <is>
           <t>古河電気工業出身の工学博士（元研究開発部技師長）が技術顧問として長年指導。社会人ドクター取得を会社として後押しする土壌がある</t>
         </is>
       </c>
-      <c r="C67" s="103" t="inlineStr">
+      <c r="C67" s="114" t="inlineStr">
         <is>
           <t>学位論文謝辞</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="102" t="inlineStr">
+      <c r="A68" s="112" t="inlineStr">
         <is>
           <t>共同研究チームの存在</t>
         </is>
       </c>
-      <c r="B68" s="103" t="inlineStr">
+      <c r="B68" s="114" t="inlineStr">
         <is>
           <t>製品開発課の同僚（新井真人係長、藤井慎太朗氏ほか）が実験全般を推進し、社会人ドクターの研究をチームでサポート。1人で抱え込まず組織的に取り組む文化</t>
         </is>
       </c>
-      <c r="C68" s="103" t="inlineStr">
+      <c r="C68" s="114" t="inlineStr">
         <is>
           <t>学位論文謝辞</t>
         </is>
@@ -3124,12 +3134,13 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" s="70">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="111" t="inlineStr">
         <is>
           <t>※「中核人材ペルソナ（案）」シートの根拠情報（本人インタビュー、学位論文、製品開発課の理念資料）を統合し、求人票・面接評価票に転用できる形に要件化したもの。第2回コンサルティング（採用基準の言語化）でのたたき台。</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="70">
       <c r="A4" s="108" t="inlineStr">
         <is>
@@ -3153,31 +3164,32 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="70">
-      <c r="A6" s="102" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>ポジション名</t>
         </is>
       </c>
       <c r="B6" s="102" t="inlineStr"/>
-      <c r="C6" s="103" t="inlineStr">
+      <c r="C6" s="114" t="inlineStr">
         <is>
           <t>製品開発課 中核技術者（将来の技術系幹部候補）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" s="70">
-      <c r="A7" s="102" t="inlineStr">
+      <c r="A7" s="112" t="inlineStr">
         <is>
           <t>募集背景</t>
         </is>
       </c>
       <c r="B7" s="102" t="inlineStr"/>
-      <c r="C7" s="103" t="inlineStr">
+      <c r="C7" s="114" t="inlineStr">
         <is>
           <t>技術習得に10～20年を要する専門分野（特殊銅合金）において、現工場長・取締役（技術系トップ）の後継となる中核人材を、中長期的な視点で確保する</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="22" customHeight="1" s="70">
       <c r="A9" s="108" t="inlineStr">
         <is>
@@ -3205,56 +3217,57 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="70">
-      <c r="A11" s="102" t="inlineStr">
+      <c r="A11" s="112" t="inlineStr">
         <is>
           <t>学歴</t>
         </is>
       </c>
-      <c r="B11" s="109" t="inlineStr">
+      <c r="B11" s="121" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C11" s="103" t="inlineStr">
+      <c r="C11" s="114" t="inlineStr">
         <is>
           <t>理工系（材料工学・金属工学・機械材料系）修士以上</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1" s="70">
-      <c r="A12" s="102" t="inlineStr">
+      <c r="A12" s="112" t="inlineStr">
         <is>
           <t>専門分野</t>
         </is>
       </c>
-      <c r="B12" s="109" t="inlineStr">
+      <c r="B12" s="121" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C12" s="103" t="inlineStr">
+      <c r="C12" s="114" t="inlineStr">
         <is>
           <t>非鉄金属材料（特に銅合金）に関する知識、または金属材料全般の基礎知識。化学成分分析（原子吸光分析等）や機械的性質・導電率検査など、分析・検査の実務経験があれば理解が早い</t>
         </is>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" s="70">
-      <c r="A13" s="102" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t>志向性</t>
         </is>
       </c>
-      <c r="B13" s="109" t="inlineStr">
+      <c r="B13" s="121" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C13" s="103" t="inlineStr">
+      <c r="C13" s="114" t="inlineStr">
         <is>
           <t>実務課題を科学的・体系的に掘り下げることに関心がある（研究開発志向）</t>
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1" s="70">
       <c r="A15" s="108" t="inlineStr">
         <is>
@@ -3282,56 +3295,57 @@
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" s="70">
-      <c r="A17" s="102" t="inlineStr">
+      <c r="A17" s="112" t="inlineStr">
         <is>
           <t>学位</t>
         </is>
       </c>
-      <c r="B17" s="110" t="inlineStr">
+      <c r="B17" s="115" t="inlineStr">
         <is>
           <t>歓迎</t>
         </is>
       </c>
-      <c r="C17" s="103" t="inlineStr">
+      <c r="C17" s="114" t="inlineStr">
         <is>
           <t>博士号（工学）取得者、または社会人ドクターとして取得する意欲がある人</t>
         </is>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1" s="70">
-      <c r="A18" s="102" t="inlineStr">
+      <c r="A18" s="112" t="inlineStr">
         <is>
           <t>研究発表経験</t>
         </is>
       </c>
-      <c r="B18" s="110" t="inlineStr">
+      <c r="B18" s="115" t="inlineStr">
         <is>
           <t>歓迎</t>
         </is>
       </c>
-      <c r="C18" s="103" t="inlineStr">
+      <c r="C18" s="114" t="inlineStr">
         <is>
           <t>学会発表・論文執筆・特許出願のいずれかの経験（ロールモデル：現工場長は査読付き論文2報・国際会議論文1報・特許共同出願を実績として保有）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1" s="70">
-      <c r="A19" s="102" t="inlineStr">
+      <c r="A19" s="112" t="inlineStr">
         <is>
           <t>対外共同研究経験</t>
         </is>
       </c>
-      <c r="B19" s="110" t="inlineStr">
+      <c r="B19" s="115" t="inlineStr">
         <is>
           <t>歓迎</t>
         </is>
       </c>
-      <c r="C19" s="103" t="inlineStr">
+      <c r="C19" s="114" t="inlineStr">
         <is>
           <t>大手企業・公的研究機関等、社外の専門家と対等に議論しながらプロジェクトを推進した経験</t>
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="22" customHeight="1" s="70">
       <c r="A21" s="108" t="inlineStr">
         <is>
@@ -3359,73 +3373,74 @@
       </c>
     </row>
     <row r="23" ht="45" customHeight="1" s="70">
-      <c r="A23" s="102" t="inlineStr">
+      <c r="A23" s="112" t="inlineStr">
         <is>
           <t>製品開発課バリューへの共感</t>
         </is>
       </c>
-      <c r="B23" s="109" t="inlineStr">
+      <c r="B23" s="121" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C23" s="103" t="inlineStr">
+      <c r="C23" s="114" t="inlineStr">
         <is>
           <t>①再現性の追求（技術的エビデンス重視）　②記録の徹底　③完遂へのこだわり　の3つに共感できること</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1" s="70">
-      <c r="A24" s="102" t="inlineStr">
+      <c r="A24" s="112" t="inlineStr">
         <is>
           <t>必須資質（優先順位）</t>
         </is>
       </c>
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="121" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C24" s="103" t="inlineStr">
+      <c r="C24" s="114" t="inlineStr">
         <is>
           <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢　＞　③立場の違う相手と対等に議論できる度胸</t>
         </is>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" s="70">
-      <c r="A25" s="102" t="inlineStr">
+      <c r="A25" s="112" t="inlineStr">
         <is>
           <t>失敗への向き合い方</t>
         </is>
       </c>
-      <c r="B25" s="109" t="inlineStr">
+      <c r="B25" s="121" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C25" s="103" t="inlineStr">
+      <c r="C25" s="114" t="inlineStr">
         <is>
           <t>失敗から逃げず、原因を追究できること（「任せられる」と判断する最重要ポイント）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" s="70">
-      <c r="A26" s="102" t="inlineStr">
+      <c r="A26" s="112" t="inlineStr">
         <is>
           <t>NG基準</t>
         </is>
       </c>
-      <c r="B26" s="109" t="inlineStr">
+      <c r="B26" s="121" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
       </c>
-      <c r="C26" s="103" t="inlineStr">
+      <c r="C26" s="114" t="inlineStr">
         <is>
           <t>都合の悪い情報を隠す、報告を遅らせる姿勢が見られる人は不可</t>
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="22" customHeight="1" s="70">
       <c r="A28" s="108" t="inlineStr">
         <is>
@@ -3449,44 +3464,45 @@
       </c>
     </row>
     <row r="30" ht="85" customHeight="1" s="70">
-      <c r="A30" s="102" t="inlineStr">
+      <c r="A30" s="112" t="inlineStr">
         <is>
           <t>入社～3年</t>
         </is>
       </c>
       <c r="B30" s="102" t="inlineStr"/>
-      <c r="C30" s="103" t="inlineStr">
+      <c r="C30" s="114" t="inlineStr">
         <is>
           <t>製造・品質保証など現場配属で「モノづくりの基盤」を体得。（ロールモデル例：溶解係で原料・合金要素の性質を体得 → 品質保証（検査）で原子吸光分析・機械的性質検査・導電率検査を担当し組織と強度のバラつきに向き合う → 砂型鋳造係で凝固過程と結晶粒組織の関係を体得し、鋳型作りから出荷までの一貫工程で納期遵守の重要性を学ぶ）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1" s="70">
-      <c r="A31" s="102" t="inlineStr">
+      <c r="A31" s="112" t="inlineStr">
         <is>
           <t>5～10年</t>
         </is>
       </c>
       <c r="B31" s="102" t="inlineStr"/>
-      <c r="C31" s="103" t="inlineStr">
+      <c r="C31" s="114" t="inlineStr">
         <is>
           <t>複数部門（製造・品質・開発等）を経験しながら、社外との共同研究機会を通じて対外折衝力を養成</t>
         </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1" s="70">
-      <c r="A32" s="102" t="inlineStr">
+      <c r="A32" s="112" t="inlineStr">
         <is>
           <t>10～20年</t>
         </is>
       </c>
       <c r="B32" s="102" t="inlineStr"/>
-      <c r="C32" s="103" t="inlineStr">
+      <c r="C32" s="114" t="inlineStr">
         <is>
           <t>製品開発課の中核技術者として自立。必要に応じ社会人ドクターとして学位取得、技術の体系化・発信を担う</t>
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="22" customHeight="1" s="70">
       <c r="A34" s="108" t="inlineStr">
         <is>
@@ -3510,44 +3526,45 @@
       </c>
     </row>
     <row r="36" ht="35" customHeight="1" s="70">
-      <c r="A36" s="102" t="inlineStr">
+      <c r="A36" s="112" t="inlineStr">
         <is>
           <t>短期（2～3ヶ月）</t>
         </is>
       </c>
       <c r="B36" s="102" t="inlineStr"/>
-      <c r="C36" s="103" t="inlineStr">
+      <c r="C36" s="114" t="inlineStr">
         <is>
           <t>仮説検証の完了数（失敗して条件を否定できたことも成果としてカウント）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="35" customHeight="1" s="70">
-      <c r="A37" s="102" t="inlineStr">
+      <c r="A37" s="112" t="inlineStr">
         <is>
           <t>中期（半年～1年）</t>
         </is>
       </c>
       <c r="B37" s="102" t="inlineStr"/>
-      <c r="C37" s="103" t="inlineStr">
+      <c r="C37" s="114" t="inlineStr">
         <is>
           <t>新価値の「型」の市場投入数（スペック承認・特許出願・ノウハウ登録等）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="35" customHeight="1" s="70">
-      <c r="A38" s="102" t="inlineStr">
+      <c r="A38" s="112" t="inlineStr">
         <is>
           <t>長期（3年～）</t>
         </is>
       </c>
       <c r="B38" s="102" t="inlineStr"/>
-      <c r="C38" s="103" t="inlineStr">
+      <c r="C38" s="114" t="inlineStr">
         <is>
           <t>競争優位のポートフォリオへの貢献（開発テーマが継続的に動いている状態の維持）</t>
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="22" customHeight="1" s="70">
       <c r="A40" s="108" t="inlineStr">
         <is>
@@ -3571,70 +3588,71 @@
       </c>
     </row>
     <row r="42" ht="35" customHeight="1" s="70">
-      <c r="A42" s="102" t="inlineStr">
+      <c r="A42" s="112" t="inlineStr">
         <is>
           <t>失敗への向き合い方</t>
         </is>
       </c>
       <c r="B42" s="102" t="inlineStr"/>
-      <c r="C42" s="103" t="inlineStr">
+      <c r="C42" s="114" t="inlineStr">
         <is>
           <t>「過去の失敗で、原因を最後まで追究した経験を教えてください」</t>
         </is>
       </c>
     </row>
     <row r="43" ht="55" customHeight="1" s="70">
-      <c r="A43" s="102" t="inlineStr">
+      <c r="A43" s="112" t="inlineStr">
         <is>
           <t>現場主義</t>
         </is>
       </c>
       <c r="B43" s="102" t="inlineStr"/>
-      <c r="C43" s="103" t="inlineStr">
+      <c r="C43" s="114" t="inlineStr">
         <is>
           <t>「データや報告だけでなく、自分の目で現場を確かめに行った経験はありますか」／「自分の部門の都合だけでなく、前工程・後工程への影響を考えて動いた経験はありますか」</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1" s="70">
-      <c r="A44" s="102" t="inlineStr">
+      <c r="A44" s="112" t="inlineStr">
         <is>
           <t>対話力・度胸</t>
         </is>
       </c>
       <c r="B44" s="102" t="inlineStr"/>
-      <c r="C44" s="103" t="inlineStr">
+      <c r="C44" s="114" t="inlineStr">
         <is>
           <t>「専門分野の異なる相手（他社・研究機関等）と議論し、意見が対立した経験はありますか」</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1" s="70">
-      <c r="A45" s="102" t="inlineStr">
+      <c r="A45" s="112" t="inlineStr">
         <is>
           <t>記録・完遂への姿勢</t>
         </is>
       </c>
       <c r="B45" s="102" t="inlineStr"/>
-      <c r="C45" s="103" t="inlineStr">
+      <c r="C45" s="114" t="inlineStr">
         <is>
           <t>「途中で頓挫しそうになったタスクを、最後までやり切った経験を教えてください」</t>
         </is>
       </c>
     </row>
     <row r="46" ht="35" customHeight="1" s="70">
-      <c r="A46" s="102" t="inlineStr">
+      <c r="A46" s="112" t="inlineStr">
         <is>
           <t>誠実性（NG基準の裏取り）</t>
         </is>
       </c>
       <c r="B46" s="102" t="inlineStr"/>
-      <c r="C46" s="103" t="inlineStr">
+      <c r="C46" s="114" t="inlineStr">
         <is>
           <t>「都合の悪い報告を、誰にどのタイミングで伝えましたか」</t>
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48" ht="22" customHeight="1" s="70">
       <c r="A48" s="108" t="inlineStr">
         <is>
@@ -3645,7 +3663,7 @@
       <c r="C48" s="107" t="n"/>
     </row>
     <row r="49" ht="95" customHeight="1" s="70">
-      <c r="A49" s="103" t="inlineStr">
+      <c r="A49" s="114" t="inlineStr">
         <is>
           <t>製造（溶解係）→品質保証（検査：原子吸光分析・機械的性質・導電率）→製造（砂型鋳造係）→製品開発課（係長）→朝霞工場長→取締役本社工場長。修士卒で入社後、在籍しながら社会人ドクターとして宇都宮大学で博士号（工学）を取得（2014年）。製品開発課係長時代にITER（核融合炉）向け銅合金の国家研究機関との共同開発、本田技研工業とのF1エンジン用コンロッドメタル共同開発・特許共同出願を実現し、朝霞工場長時代には2S活動・生産性改善で現場改革を主導。現場経験を土台に外部と対等に渡り合う技術者として成長した実例。詳細は「中核人材ペルソナ（案）」シートを参照。</t>
         </is>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -2192,7 +2192,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1" s="70">
+    <row r="2" ht="41.3" customHeight="1" s="70">
       <c r="A2" s="111" t="inlineStr">
         <is>
           <t>※第2回コンサルティング（中核人材ペルソナ設計と採用基準の言語化）での使用を想定した素案。本人インタビューおよび「製品開発課の理念」「ミッション・ビジョン・バリュー」「何を成果とみなすか」の社内資料をもとに作成。</t>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1" s="70">
+    <row r="14" ht="133" customHeight="1" s="70">
       <c r="A14" s="112" t="inlineStr">
         <is>
           <t>博士論文テーマ</t>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1" s="70">
+    <row r="26" ht="41.3" customHeight="1" s="70">
       <c r="A26" s="112" t="inlineStr">
         <is>
           <t>現在の強み</t>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="41.3" customHeight="1" s="70">
       <c r="A31" s="112" t="inlineStr">
         <is>
           <t>必須の資質（優先順位順）</t>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="41.3" customHeight="1" s="70">
       <c r="A42" s="112" t="inlineStr">
         <is>
           <t>ミッション</t>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1" s="70">
+    <row r="44" ht="41.3" customHeight="1" s="70">
       <c r="A44" s="112" t="inlineStr">
         <is>
           <t>バリュー（3つ）</t>
@@ -2789,7 +2789,7 @@
       <c r="B47" s="106" t="n"/>
       <c r="C47" s="107" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="22.9" customHeight="1" s="70">
       <c r="A48" s="101" t="inlineStr">
         <is>
           <t>項目</t>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1" s="70">
+    <row r="49" ht="41.3" customHeight="1" s="70">
       <c r="A49" s="112" t="inlineStr">
         <is>
           <t>短期成果（2～3ヶ月）</t>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1" s="70">
+    <row r="51" ht="41.3" customHeight="1" s="70">
       <c r="A51" s="112" t="inlineStr">
         <is>
           <t>育成初期の目標設計への示唆</t>
@@ -2944,7 +2944,7 @@
       <c r="B58" s="106" t="n"/>
       <c r="C58" s="107" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="22.9" customHeight="1" s="70">
       <c r="A59" s="101" t="inlineStr">
         <is>
           <t>項目</t>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="75" customHeight="1" s="70">
+    <row r="60" ht="96.3" customHeight="1" s="70">
       <c r="A60" s="112" t="inlineStr">
         <is>
           <t>査読付き学術論文（筆頭著者・全2報）</t>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1" s="70">
+    <row r="61" ht="114.7" customHeight="1" s="70">
       <c r="A61" s="112" t="inlineStr">
         <is>
           <t>国際会議論文（筆頭著者）</t>
@@ -3024,7 +3024,7 @@
       <c r="B64" s="106" t="n"/>
       <c r="C64" s="107" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="22.9" customHeight="1" s="70">
       <c r="A65" s="101" t="inlineStr">
         <is>
           <t>項目</t>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="59.6" customHeight="1" s="70">
       <c r="A66" s="112" t="inlineStr">
         <is>
           <t>経営陣も博士号取得者</t>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="41.3" customHeight="1" s="70">
       <c r="A67" s="112" t="inlineStr">
         <is>
           <t>社外の技術顧問体制</t>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="59.6" customHeight="1" s="70">
       <c r="A68" s="112" t="inlineStr">
         <is>
           <t>共同研究チームの存在</t>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1" s="70">
+    <row r="2" ht="41.3" customHeight="1" s="70">
       <c r="A2" s="111" t="inlineStr">
         <is>
           <t>※「中核人材ペルソナ（案）」シートの根拠情報（本人インタビュー、学位論文、製品開発課の理念資料）を統合し、求人票・面接評価票に転用できる形に要件化したもの。第2回コンサルティング（採用基準の言語化）でのたたき台。</t>
@@ -3713,13 +3713,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="70">
+    <row r="2" ht="41.3" customHeight="1" s="70">
       <c r="A2" s="111" t="inlineStr">
         <is>
           <t>※共通シリーズ名「売上100億円を目指す中小企業経営者のための人材戦略」。各講師のPDFシラバス（アップロードされた第2・3・4・6・7・8回分）をもとに要約。第1回・第5回のシラバスは未取得。</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="70">
       <c r="A4" s="101" t="inlineStr">
         <is>
@@ -3958,6 +3959,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="55" customHeight="1" s="70">
       <c r="A12" s="111" t="inlineStr">
         <is>
@@ -4004,6 +4006,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="70">
       <c r="A4" s="101" t="inlineStr">
         <is>
@@ -4164,6 +4167,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="40" customHeight="1" s="70">
       <c r="A12" s="120" t="inlineStr">
         <is>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F4" s="77" t="n"/>
     </row>
-    <row r="5" ht="27.95" customHeight="1" s="70">
+    <row r="5" ht="84.59999999999999" customHeight="1" s="70">
       <c r="A5" s="45" t="inlineStr">
         <is>
           <t>【１００億宣言の申請状況】　１００億宣言企業（単独申請）
@@ -1831,7 +1831,7 @@
       <c r="E9" s="72" t="n"/>
       <c r="F9" s="73" t="n"/>
     </row>
-    <row r="10" ht="174.6" customHeight="1" s="70">
+    <row r="10" ht="224.7" customHeight="1" s="70">
       <c r="A10" s="82" t="inlineStr">
         <is>
           <t>改善計画及び方向性（採用A「採用戦略構築」）　※採用B「採用テクニック」も一部補完していく。
@@ -1917,7 +1917,7 @@
       <c r="E14" s="72" t="n"/>
       <c r="F14" s="73" t="n"/>
     </row>
-    <row r="15" ht="48.6" customHeight="1" s="70">
+    <row r="15" ht="64.59999999999999" customHeight="1" s="70">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>第１回</t>

--- a/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
+++ b/【大和合金様】 コンサルティング実施計画書_提出日0915.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="コンサルティング実施計画書（大和合金株式会社）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="中核人材ペルソナ（案）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="後継者ペルソナ要件（案）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="オンラインセミナー講師一覧" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="人材確保の要点（まとめ）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コンサルティング実施計画書（大和合金株式会社）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中核人材ペルソナ（案）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="後継者ペルソナ要件（案）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="オンラインセミナー講師一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人材確保の要点（まとめ）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'コンサルティング実施計画書（大和合金株式会社）'!$A$1:$F$23</definedName>
@@ -951,7 +951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1281,6 +1281,9 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="9" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2177,7 +2180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="70" min="1" max="1"/>
@@ -2572,7 +2575,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="41.3" customHeight="1" s="70">
+    <row r="31" ht="95" customHeight="1" s="70">
       <c r="A31" s="112" t="inlineStr">
         <is>
           <t>必須の資質（優先順位順）</t>
@@ -2580,16 +2583,17 @@
       </c>
       <c r="B31" s="114" t="inlineStr">
         <is>
-          <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢（現場主義）　＞　③立場の違う人と対等に議論できる度胸</t>
+          <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢（現場主義）　＞　③立場の違う人と対等に議論できる度胸
+＋（致知感想文の裏付けより）④内省・自責（他責にしない）　⑤拙速を尊ぶ（評論家・傍観者にならず行動する）　⑥利他の心（損得抜きの気配り）</t>
         </is>
       </c>
       <c r="C31" s="114" t="inlineStr">
         <is>
-          <t>本人インタビュー</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="40" customHeight="1" s="70">
+          <t>本人インタビュー＋Obsidian「私の哲学」（致知感想文2018〜2026年、6テーマ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1" s="70">
       <c r="A32" s="112" t="inlineStr">
         <is>
           <t>「任せられる」と判断する決め手</t>
@@ -2597,12 +2601,12 @@
       </c>
       <c r="B32" s="114" t="inlineStr">
         <is>
-          <t>失敗への向き合い方（逃げずに原因を追究できるか）</t>
+          <t>失敗への向き合い方（逃げずに原因を追究できるか）。致知感想文「内省・自責」テーマと直結：うまくいかない時に人や環境のせいにせず、自分に矢印を向けられるか。2018〜2026年で最も繰り返し立ち返っている価値観の一つ</t>
         </is>
       </c>
       <c r="C32" s="114" t="inlineStr">
         <is>
-          <t>本人インタビュー</t>
+          <t>本人インタビュー＋Obsidian「私の哲学／内省・自責（他責にしない）」</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2644,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="22" customHeight="1" s="70">
       <c r="A36" s="105" t="inlineStr">
         <is>
@@ -3092,14 +3095,151 @@
         </is>
       </c>
     </row>
+    <row r="70" ht="22" customHeight="1" s="70">
+      <c r="A70" s="105" t="inlineStr">
+        <is>
+          <t>K. 致知感想文にみる根底の価値観（2018〜2026年、Obsidian「私の哲学」より）</t>
+        </is>
+      </c>
+      <c r="B70" s="106" t="n"/>
+      <c r="C70" s="107" t="n"/>
+    </row>
+    <row r="71" ht="20" customHeight="1" s="70">
+      <c r="A71" s="101" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B71" s="101" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C71" s="101" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="80" customHeight="1" s="70">
+      <c r="A72" s="112" t="inlineStr">
+        <is>
+          <t>利他の心</t>
+        </is>
+      </c>
+      <c r="B72" s="114" t="inlineStr">
+        <is>
+          <t>損得抜きの気配り・小さな善を見過ごさない姿勢が2018年から一貫。近年は「良い会社とは何か」という経営的な問いに接続（「すさんだ心の集団、会社ほど悲惨なものはない」）</t>
+        </is>
+      </c>
+      <c r="C72" s="114" t="inlineStr">
+        <is>
+          <t>Obsidian「私の哲学／利他の心」</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="80" customHeight="1" s="70">
+      <c r="A73" s="112" t="inlineStr">
+        <is>
+          <t>継続する力</t>
+        </is>
+      </c>
+      <c r="B73" s="114" t="inlineStr">
+        <is>
+          <t>計画通りいかなくても立ち止まって直し、また歩き出す。開発力向上プロジェクトの製品開発課バリュー「完遂へのこだわり」を本人が自ら接続づけている（ドラッカー「中断してはならない」引用）</t>
+        </is>
+      </c>
+      <c r="C73" s="114" t="inlineStr">
+        <is>
+          <t>Obsidian「私の哲学／継続する力」</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="80" customHeight="1" s="70">
+      <c r="A74" s="112" t="inlineStr">
+        <is>
+          <t>出逢い・縁を生かす</t>
+        </is>
+      </c>
+      <c r="B74" s="114" t="inlineStr">
+        <is>
+          <t>偶然の出逢いを生かせるかは受け取る側の準備・感度次第という捉え方。柳生家家訓「大才は袖すり合った縁を生かす」。ITER・Honda F1の共同開発実績も、この「縁を生かす」感度の一例と解釈できる</t>
+        </is>
+      </c>
+      <c r="C74" s="114" t="inlineStr">
+        <is>
+          <t>Obsidian「私の哲学／出逢い・縁を生かす」</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="90" customHeight="1" s="70">
+      <c r="A75" s="112" t="inlineStr">
+        <is>
+          <t>人を育てるということ</t>
+        </is>
+      </c>
+      <c r="B75" s="114" t="inlineStr">
+        <is>
+          <t>教えることを負担でなく知識循環・組織成長の手段と捉える。率先垂範。開発力向上プロジェクトを通じ「この理念を未来に受け継いでもらうためには、正しい理解と対話が重要」と明言（2026年5月号感想文）</t>
+        </is>
+      </c>
+      <c r="C75" s="114" t="inlineStr">
+        <is>
+          <t>Obsidian「私の哲学／人を育てるということ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="90" customHeight="1" s="70">
+      <c r="A76" s="112" t="inlineStr">
+        <is>
+          <t>拙速を尊ぶ</t>
+        </is>
+      </c>
+      <c r="B76" s="114" t="inlineStr">
+        <is>
+          <t>「巧遅は拙速に如かず」。鶴田常務・相談役から直接授けられた言葉として8年近く繰り返し立ち返る。2026年に「熟慮断行」と統合＝平時は熟慮を絶えず行い、実行段階では拙速（スピード）を優先</t>
+        </is>
+      </c>
+      <c r="C76" s="114" t="inlineStr">
+        <is>
+          <t>Obsidian「私の哲学／拙速を尊ぶ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="90" customHeight="1" s="70">
+      <c r="A77" s="112" t="inlineStr">
+        <is>
+          <t>内省・自責（他責にしない）</t>
+        </is>
+      </c>
+      <c r="B77" s="114" t="inlineStr">
+        <is>
+          <t>うまくいかない時に人や環境のせいにせず、自分に矢印を向ける。2018年から2026年まで最も繰り返し立ち返る価値観の一つ。「傍観者や評論家となって行動しないこと」を強く戒めている</t>
+        </is>
+      </c>
+      <c r="C77" s="114" t="inlineStr">
+        <is>
+          <t>Obsidian「私の哲学／内省・自責（他責にしない）」</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="45" customHeight="1" s="70">
+      <c r="A79" s="122" t="inlineStr">
+        <is>
+          <t>【後継者要件への示唆】上記6つは断片的な美徳ではなく、8年間の一貫した実践から立ち上がった価値観であり、D章「後継者に求める資質」と合わせて、採用面接・育成計画の判断軸として活用できる。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A79:C79"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A12:C12"/>
@@ -3118,7 +3258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="70" min="1" max="1"/>
@@ -3140,7 +3280,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="70">
       <c r="A4" s="108" t="inlineStr">
         <is>
@@ -3189,7 +3328,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="22" customHeight="1" s="70">
       <c r="A9" s="108" t="inlineStr">
         <is>
@@ -3267,7 +3405,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="22" customHeight="1" s="70">
       <c r="A15" s="108" t="inlineStr">
         <is>
@@ -3345,7 +3482,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="22" customHeight="1" s="70">
       <c r="A21" s="108" t="inlineStr">
         <is>
@@ -3389,7 +3525,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1" s="70">
+    <row r="24" ht="70" customHeight="1" s="70">
       <c r="A24" s="112" t="inlineStr">
         <is>
           <t>必須資質（優先順位）</t>
@@ -3402,11 +3538,12 @@
       </c>
       <c r="C24" s="114" t="inlineStr">
         <is>
-          <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢　＞　③立場の違う相手と対等に議論できる度胸</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="35" customHeight="1" s="70">
+          <t>①地道な努力を長期的に継続できる忍耐力　＞　②現場を自分の目で見に行く姿勢　＞　③立場の違う相手と対等に議論できる度胸
+＋ ④内省・自責（他責にしない）　⑤拙速を尊ぶ（行動力・実行主義）　⑥利他の心（損得抜きの気配り）※本人が8年間一貫して大切にしてきた価値観（致知感想文より）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1" s="70">
       <c r="A25" s="112" t="inlineStr">
         <is>
           <t>失敗への向き合い方</t>
@@ -3419,7 +3556,7 @@
       </c>
       <c r="C25" s="114" t="inlineStr">
         <is>
-          <t>失敗から逃げず、原因を追究できること（「任せられる」と判断する最重要ポイント）</t>
+          <t>失敗から逃げず、原因を追究できること（「任せられる」と判断する最重要ポイント）。本人の言葉では「うまくいかない時に人や環境のせいにせず、自分に矢印を向けられるか」</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3577,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="22" customHeight="1" s="70">
       <c r="A28" s="108" t="inlineStr">
         <is>
@@ -3502,7 +3638,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="22" customHeight="1" s="70">
       <c r="A34" s="108" t="inlineStr">
         <is>
@@ -3564,7 +3699,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="22" customHeight="1" s="70">
       <c r="A40" s="108" t="inlineStr">
         <is>
@@ -3652,7 +3786,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48" ht="22" customHeight="1" s="70">
       <c r="A48" s="108" t="inlineStr">
         <is>
@@ -3671,8 +3804,106 @@
       <c r="B49" s="106" t="n"/>
       <c r="C49" s="107" t="n"/>
     </row>
+    <row r="51" ht="22" customHeight="1" s="70">
+      <c r="A51" s="108" t="inlineStr">
+        <is>
+          <t>I. 追加の面接質問例（本人の哲学「致知感想文」より、2026年9月22日追記）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" s="70">
+      <c r="A52" s="101" t="inlineStr">
+        <is>
+          <t>確認したい資質</t>
+        </is>
+      </c>
+      <c r="B52" s="101" t="inlineStr"/>
+      <c r="C52" s="101" t="inlineStr">
+        <is>
+          <t>質問例</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1" s="70">
+      <c r="A53" s="112" t="inlineStr">
+        <is>
+          <t>継続する力</t>
+        </is>
+      </c>
+      <c r="B53" s="114" t="n"/>
+      <c r="C53" s="114" t="inlineStr">
+        <is>
+          <t>「計画通りにいかなかった時、どのように立て直しましたか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1" s="70">
+      <c r="A54" s="112" t="inlineStr">
+        <is>
+          <t>拙速を尊ぶ</t>
+        </is>
+      </c>
+      <c r="B54" s="114" t="n"/>
+      <c r="C54" s="114" t="inlineStr">
+        <is>
+          <t>「完璧でなくても素早く動いた経験、逆に動きすぎて後悔した経験はありますか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1" s="70">
+      <c r="A55" s="112" t="inlineStr">
+        <is>
+          <t>利他の心</t>
+        </is>
+      </c>
+      <c r="B55" s="114" t="n"/>
+      <c r="C55" s="114" t="inlineStr">
+        <is>
+          <t>「損得抜きに、周囲への小さな配慮をした経験を教えてください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1" s="70">
+      <c r="A56" s="112" t="inlineStr">
+        <is>
+          <t>出逢い・縁を生かす</t>
+        </is>
+      </c>
+      <c r="B56" s="114" t="n"/>
+      <c r="C56" s="114" t="inlineStr">
+        <is>
+          <t>「偶然の出会いや出来事が、仕事の転機になった経験はありますか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1" s="70">
+      <c r="A57" s="112" t="inlineStr">
+        <is>
+          <t>人を育てるということ</t>
+        </is>
+      </c>
+      <c r="B57" s="114" t="n"/>
+      <c r="C57" s="114" t="inlineStr">
+        <is>
+          <t>「人に教える・後輩を育てることを、どのように捉えていますか」</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="55" customHeight="1" s="70">
+      <c r="A58" s="112" t="inlineStr">
+        <is>
+          <t>内省・自責（再確認）</t>
+        </is>
+      </c>
+      <c r="B58" s="114" t="n"/>
+      <c r="C58" s="114" t="inlineStr">
+        <is>
+          <t>「うまくいかなかった時、環境や他人のせいにせず、自分に矢印を向けられていますか。具体例を教えてください」</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A1:C1"/>
@@ -3684,6 +3915,7 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A51:C51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3720,7 +3952,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="70">
       <c r="A4" s="101" t="inlineStr">
         <is>
@@ -3959,7 +4190,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="55" customHeight="1" s="70">
       <c r="A12" s="111" t="inlineStr">
         <is>
@@ -4006,7 +4236,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="70">
       <c r="A4" s="101" t="inlineStr">
         <is>
@@ -4167,7 +4396,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="40" customHeight="1" s="70">
       <c r="A12" s="120" t="inlineStr">
         <is>
